--- a/DOCS/CUADRO CLINICO.xlsx
+++ b/DOCS/CUADRO CLINICO.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Masframe\masesora_backend\DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCA247A-43FD-4D11-A9B3-010B0CC7B98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE27612F-4CFB-4D3F-91DF-96032A6E947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="752" xr2:uid="{D6E07D98-3F80-4C8B-815A-0E0596533566}"/>
+    <workbookView xWindow="11940" yWindow="300" windowWidth="16860" windowHeight="11760" tabRatio="752" activeTab="4" xr2:uid="{D6E07D98-3F80-4C8B-815A-0E0596533566}"/>
   </bookViews>
   <sheets>
-    <sheet name="PROMTP ARTEFACTO" sheetId="7" r:id="rId1"/>
-    <sheet name="CC (base)" sheetId="3" r:id="rId2"/>
-    <sheet name="kpis MAESTROS (por poner aldía)" sheetId="2" r:id="rId3"/>
-    <sheet name="100" sheetId="4" r:id="rId4"/>
-    <sheet name="CC PIES " sheetId="6" r:id="rId5"/>
-    <sheet name="UCI FINANCIERA" sheetId="5" r:id="rId6"/>
+    <sheet name="CC (base)" sheetId="3" r:id="rId1"/>
+    <sheet name="kpis MAESTROS (por poner aldía)" sheetId="2" r:id="rId2"/>
+    <sheet name="100" sheetId="4" r:id="rId3"/>
+    <sheet name="CC PIES " sheetId="6" r:id="rId4"/>
+    <sheet name="UCI FINANCIERA" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'100'!$A$1:$AD$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'100'!$A$1:$AD$101</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4060" uniqueCount="3504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3764" uniqueCount="3243">
   <si>
     <t>OPE-S10</t>
   </si>
@@ -11305,831 +11304,6 @@
   </si>
   <si>
     <t>RESCATE DE PERSONAS</t>
-  </si>
-  <si>
-    <t>LO QUE NECESITO CREAR:  UN artefacto + biblioteca de herramientas\*\*</t>
-  </si>
-  <si>
-    <t>Renderiza contenido específico0 herramientas</t>
-  </si>
-  <si>
-    <t>// Renderizado dinámico</t>
-  </si>
-  <si>
-    <t>const Tool = ToolLibrary\[symptom.herramienta];</t>
-  </si>
-  <si>
-    <t>return &lt;Tool data={symptomData} /&gt;;</t>
-  </si>
-  <si>
-    <t>// COMPONENTE BASE UNIVERSAL (200 líneas)</t>
-  </si>
-  <si>
-    <t>const DashboardUniversal = ({ config }) =&gt; {</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; const {</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   titulo,</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   color,</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   kpis,           // Array de KPIs a mostrar</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   layout,         // 'grid' | 'vertical' | 'horizontal'</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   alertas,        // Umbrales de alerta</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   acciones        // Botones de acción</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; } = config;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; return (</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   &lt;div className={`dashboard ${color}`}&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     &lt;h1&gt;{titulo}&lt;/h1&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;nbsp;     </t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     {/\* Motor genérico de KPIs \*/}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     &lt;div className={`layout-${layout}`}&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;       {kpis.map(kpi =&gt; (</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;nbsp;         &lt;KPICard </t>
-  </si>
-  <si>
-    <t>&amp;nbsp;           key={kpi.id}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;           nombre={kpi.nombre}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;           valor={kpi.valor}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;           meta={kpi.meta}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;           alerta={alertas\[kpi.id]}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;         /&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;       ))}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     {/\* Sistema de acciones \*/}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     &lt;ActionBar acciones={acciones} /&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; );</t>
-  </si>
-  <si>
-    <t>};</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUE TENGA UN MANTENIMIENTO CENTRALIZADO PARA CREAR O MODIFICAR SUSTANCIALMENTE. </t>
-  </si>
-  <si>
-    <t>// En DashboardUniversal (1 lugar)</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; const exportarPDF = () =&gt; {</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   // Lógica de exportación</t>
-  </si>
-  <si>
-    <t>&amp;nbsp; };</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;   &lt;div&gt;</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     {/\* ... resto del código \*/}</t>
-  </si>
-  <si>
-    <t>&amp;nbsp;     &lt;button onClick={exportarPDF}&gt;📥 Exportar PDF&lt;/button&gt;</t>
-  </si>
-  <si>
-    <t>// Automáticamente TODOS los dashboards tienen el botón</t>
-  </si>
-  <si>
-    <t>```</t>
-  </si>
-  <si>
-    <t>\### \*\*3. Consistencia Visual Automática\*\*</t>
-  </si>
-  <si>
-    <t>Todos los dashboards tienen:</t>
-  </si>
-  <si>
-    <t>\- Mismo estilo</t>
-  </si>
-  <si>
-    <t>\- Mismas animaciones</t>
-  </si>
-  <si>
-    <t>\- Mismo comportamiento</t>
-  </si>
-  <si>
-    <t>\- Misma UX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\## \*\*🏗️ ARQUITECTURA DE COMPONENTES BASE\*\* ( P E N D I E N T E    D E   R E V I S A R) </t>
-  </si>
-  <si>
-    <t>DashboardUniversal</t>
-  </si>
-  <si>
-    <t>├── KPICard (tarjetas de métricas)</t>
-  </si>
-  <si>
-    <t>├── AlertSystem (sistema de alertas)</t>
-  </si>
-  <si>
-    <t>├── ActionBar (barra de acciones)</t>
-  </si>
-  <si>
-    <t>├── ChartEngine (motor de gráficos)</t>
-  </si>
-  <si>
-    <t>└── ExportModule (exportación)</t>
-  </si>
-  <si>
-    <t>MatrizUniversal</t>
-  </si>
-  <si>
-    <t>├── GridLayout (diseño de cuadrícula)</t>
-  </si>
-  <si>
-    <t>├── CellRenderer (renderizado de celdas)</t>
-  </si>
-  <si>
-    <t>├── FilterBar (barra de filtros)</t>
-  </si>
-  <si>
-    <t>└── LegendSystem (sistema de leyendas)</t>
-  </si>
-  <si>
-    <t>ChecklistDinamico</t>
-  </si>
-  <si>
-    <t>├── CheckItem (item de checklist)</t>
-  </si>
-  <si>
-    <t>├── ProgressBar (barra de progreso)</t>
-  </si>
-  <si>
-    <t>├── CompletionBadge (medalla de completado)</t>
-  </si>
-  <si>
-    <t>└── ResetButton (botón de reinicio)</t>
-  </si>
-  <si>
-    <t>CalculadoraKPIs</t>
-  </si>
-  <si>
-    <t>├── FormulaParser (interpreta fórmulas)</t>
-  </si>
-  <si>
-    <t>├── InputManager (gestión de inputs)</t>
-  </si>
-  <si>
-    <t>├── ResultDisplay (muestra resultados)</t>
-  </si>
-  <si>
-    <t>└── DeltaCalculator (calcula variaciones)</t>
-  </si>
-  <si>
-    <t>PlanificadorEstrategico</t>
-  </si>
-  <si>
-    <t>├── TimelineView (vista de línea de tiempo)</t>
-  </si>
-  <si>
-    <t>├── MilestoneCard (hitos)</t>
-  </si>
-  <si>
-    <t>├── DependencyMap (mapa de dependencias)</t>
-  </si>
-  <si>
-    <t>└── ProgressTracker (seguimiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">❌SE QUE TENGO PROBLEMAS CRÍTICOS DETECTADOS EN UN CUADRO CLINICO EN EXCEL COMO: </t>
-  </si>
-  <si>
-    <t>\- "CRM/Secuencias Automáticas" (esto es un software completo)</t>
-  </si>
-  <si>
-    <t>\- "Sistema de Automatización" (esto es una categoría entera)</t>
-  </si>
-  <si>
-    <t>\- "Integración de Sistemas" (esto es arquitectura IT)</t>
-  </si>
-  <si>
-    <t>\*\*Otros son MICRO-ACCIONES:\*\*</t>
-  </si>
-  <si>
-    <t>\- "Lista de Acciones WOW" (esto es una hoja de Excel)</t>
-  </si>
-  <si>
-    <t>\- "Hoja de Registro de Tiempo" (literalmente una tabla)</t>
-  </si>
-  <si>
-    <t>\- "Checklist de Puesta a Punto" (una lista de 10 ítems)</t>
-  </si>
-  <si>
-    <t>\## \*\*✅ LO QUE SÍ FUNCIONA\*\*</t>
-  </si>
-  <si>
-    <t>\### \*\*Aciertos de tu Framework:\*\*</t>
-  </si>
-  <si>
-    <t>1\. \*\*Estructura Decisión → Acción → Herramienta\*\* es SÓLIDA</t>
-  </si>
-  <si>
-    <t>2\. \*\*Las fórmulas de KPIs\*\* están bien pensadas (aunque algunas son muy básicas)</t>
-  </si>
-  <si>
-    <t>3\. \*\*La segmentación por departamentos\*\* es clara</t>
-  </si>
-  <si>
-    <t>4\. \*\*Los nombres de síntomas\*\* son impactantes ("Hemorragia de Caja", "Arritmia de Ventas")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NECESITO UNA AGRUPACIÓN REAL </t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 1: DASHBOARDS \&amp; VISUALIZACIÓN (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Dashboard Universal`</t>
-  </si>
-  <si>
-    <t>\*\*Configuraciones:\*\*</t>
-  </si>
-  <si>
-    <t>\- Dashboard de Mando Neuro</t>
-  </si>
-  <si>
-    <t>\- Panel de Control Ejecutivo</t>
-  </si>
-  <si>
-    <t>\- Dashboard de Autonomía</t>
-  </si>
-  <si>
-    <t>\- Dashboard de Expansión</t>
-  </si>
-  <si>
-    <t>\- Cuadro de Mandos Operativo</t>
-  </si>
-  <si>
-    <t>\- Panel de Performance</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 2: MATRICES DE CLASIFICACIÓN (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Matriz Universal 2x2 o NxN`</t>
-  </si>
-  <si>
-    <t>\- Pareto 80/20 (eje valor/volumen)</t>
-  </si>
-  <si>
-    <t>\- ABC Stock (eje criticidad/rotación)</t>
-  </si>
-  <si>
-    <t>\- Margen/Esfuerzo (eje rentabilidad/complejidad)</t>
-  </si>
-  <si>
-    <t>\- Priorización (eje impacto/esfuerzo)</t>
-  </si>
-  <si>
-    <t>\- DAFO (categorías fijas)</t>
-  </si>
-  <si>
-    <t>\- 9-Box Talento (eje desempeño/potencial)</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 3: CALCULADORAS DE CICLO (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Calculadora de Flujo Temporal`</t>
-  </si>
-  <si>
-    <t>\- Ciclo de Caja (días)</t>
-  </si>
-  <si>
-    <t>\- Ciclo de Conversión (días)</t>
-  </si>
-  <si>
-    <t>\- Velocidad de Cobro (días)</t>
-  </si>
-  <si>
-    <t>\- DPO Proveedores (días)</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 4: CHECKLISTS DINÁMICOS (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Checklist Inteligente`</t>
-  </si>
-  <si>
-    <t>\- Calidad/Handoff</t>
-  </si>
-  <si>
-    <t>\- Fricción Cero</t>
-  </si>
-  <si>
-    <t>\- Puesta a Punto</t>
-  </si>
-  <si>
-    <t>\- Sincronía</t>
-  </si>
-  <si>
-    <t>\- Primera Impresión</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 5: SISTEMAS DE PLANIFICACIÓN (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Roadmap/Timeline Universal`</t>
-  </si>
-  <si>
-    <t>\- Roadmap Estratégico</t>
-  </si>
-  <si>
-    <t>\- Plan de Rescate</t>
-  </si>
-  <si>
-    <t>\- Plan de Sucesión</t>
-  </si>
-  <si>
-    <t>\- Plan de Escalabilidad</t>
-  </si>
-  <si>
-    <t>\- Plan Multicanal</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 6: HERRAMIENTAS DE EVALUACIÓN (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Sistema de Scoring/Auditoría`</t>
-  </si>
-  <si>
-    <t>\- Test de Estrés</t>
-  </si>
-  <si>
-    <t>\- Auditoría LEAN</t>
-  </si>
-  <si>
-    <t>\- Auditoría Visual</t>
-  </si>
-  <si>
-    <t>\- eNPS</t>
-  </si>
-  <si>
-    <t>\- Cuestionarios personalizados</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 7: PROTOCOLOS Y MANUALES (1 herramienta base)\*\*</t>
-  </si>
-  <si>
-    <t>\*\*Herramienta única:\*\* `Generador de Documentación`</t>
-  </si>
-  <si>
-    <t>\- Manuales de procesos</t>
-  </si>
-  <si>
-    <t>\- Códigos de conducta</t>
-  </si>
-  <si>
-    <t>\- Guías de feedback</t>
-  </si>
-  <si>
-    <t>\- Protocolos de delegación</t>
-  </si>
-  <si>
-    <t>\#### \*\*GRUPO 8: HERRAMIENTAS ESPECÍFICAS ÚNICAS\*\*</t>
-  </si>
-  <si>
-    <t>Estas SÍ son únicas y no agrupables:</t>
-  </si>
-  <si>
-    <t>1\. \*\*Matriz de Tesorería\*\* (gestión entradas/salidas)</t>
-  </si>
-  <si>
-    <t>2\. \*\*CRM/Secuencias\*\* (esto es compra de software externo)</t>
-  </si>
-  <si>
-    <t>3\. \*\*Sistema de Automatización\*\* (esto es integración técnica)</t>
-  </si>
-  <si>
-    <t>4\. \*\*Regla 5/25\*\* (método específico de priorización)</t>
-  </si>
-  <si>
-    <t>5\. \*\*Escandallo de Oro S10\*\* (cálculo de costes)</t>
-  </si>
-  <si>
-    <t>6\. \*\*Presupuesto Cero\*\* (metodología presupuestaria)</t>
-  </si>
-  <si>
-    <t>7\. \*\*Dossier Bancario\*\* (plantilla específica)</t>
-  </si>
-  <si>
-    <t>\*\*Total real:\*\* 7 herramientas únicas</t>
-  </si>
-  <si>
-    <t>\## \*\*📊 RESUMEN BRUTAL\*\*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tengo 100 herramientas únicas = 7 Herramientas Base Universales TRAS REAGRUPAR </t>
-  </si>
-  <si>
-    <t>\+ 7 Herramientas Específicas Únicas + ~75 Archivos de Configuración</t>
-  </si>
-  <si>
-    <t>= 14 HERRAMIENTAS REALES + 86 VARIACIONES</t>
-  </si>
-  <si>
-    <t>\## \*\*🎯 RUTA ÓPTIMA REAL\*\*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEMOS REPARTIDO LOS 100 SINTOMAS ENTRE 10 ESPECIALIDADES CADA UNO, A SU VEZ EN 3 PLANES (PIE, LOS 3 PRIMEROS; PAE, LOS 6 PRIMEROS, PRE, LOS 10 EN TOTAL) </t>
-  </si>
-  <si>
-    <t>LOS PIEs VAN A SER NUESTRO MVP. NECESITO DEJAR LA ESTRUCTURA LISTA PARA ESCALAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TENEMOS QUE TERMINAR EL CUADRO CLINICO EN EXCEL PARA: </t>
-  </si>
-  <si>
-    <t>\### \*\*FASE 1: Construir los Motores Base</t>
-  </si>
-  <si>
-    <t>1\. Dashboard Universal</t>
-  </si>
-  <si>
-    <t>2\. Matriz Universal</t>
-  </si>
-  <si>
-    <t>3\. Calculadora de Flujo</t>
-  </si>
-  <si>
-    <t>4\. Checklist Dinámico</t>
-  </si>
-  <si>
-    <t>5\. Roadmap/Timeline</t>
-  </si>
-  <si>
-    <t>6\. Sistema de Scoring</t>
-  </si>
-  <si>
-    <t>7\. Generador de Docs</t>
-  </si>
-  <si>
-    <t>\### \*\*FASE 2: Construir las Herramientas Únicas</t>
-  </si>
-  <si>
-    <t>8\. Matriz de Tesorería ✅</t>
-  </si>
-  <si>
-    <t>9\. Regla 5/25</t>
-  </si>
-  <si>
-    <t>10\. Escandallo de Oro</t>
-  </si>
-  <si>
-    <t>11\. Presupuesto Cero</t>
-  </si>
-  <si>
-    <t>12\. Dossier Bancario</t>
-  </si>
-  <si>
-    <t>13\. Integración CRM (config, no desarrollo)</t>
-  </si>
-  <si>
-    <t>14\. Sistema de Automatización (config, no desarrollo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\### \*\*FASE 3: Crear el resto de Archivos de Config </t>
-  </si>
-  <si>
-    <t>\- Scripts automáticos desde tu CSV</t>
-  </si>
-  <si>
-    <t>\- Validación y testing</t>
-  </si>
-  <si>
-    <t>INFLACIÓN DE NOMENCLATURA\*\*</t>
-  </si>
-  <si>
-    <t>GRANULARIDAD INCONSISTENTE\*\*</t>
-  </si>
-  <si>
-    <t>Algunos son MEGA-HERRAMIENTAS:</t>
-  </si>
-  <si>
-    <t>HERRAMIENTAS "FANTASMA"\*\*</t>
-  </si>
-  <si>
-    <t>REDUNDANCIA MASIVA EN HERRAMIENTAS:</t>
-  </si>
-  <si>
-    <t>Paso 1 – Flujo general del wizard</t>
-  </si>
-  <si>
-    <t>Pensado para dueño de pyme, en 4 pasos máximos:​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paso 1: </t>
-  </si>
-  <si>
-    <t>Logica Masesora</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> con este plan de impulso empresarial vamos a tratar los 3 sintomas principales! _x000D_
-sintoma UCI-S1_x000D_
-input a_x000D_
-input b_x000D_
-formula _x000D_
-resultado_x000D_
-objetivo kpi _x000D_
-ejemplo _x000D_
-_x000D_
-y luego, lo mismo con los otros 2 sintomas de la especialidad.  _x000D_
-sintoma UCI-S2_x000D_
-input a_x000D_
-input b_x000D_
-...._x000D_
-sintoma UCI-S3_x000D_
-input a_x000D_
-input b_x000D_
-..._x000D_
-Campos: facturación mensual media, gastos fijos, nº empleados, sector (selector), antigüedad, modelo (servicios/producto/mixto). NO ES NECESARIO. _x000D_
-Objetivo: que el sistema pueda aplicar correctamente las fórmulas de las 30 fichas (LUEGO 70 MAS) _x000D_
-Paso 2: HERRAMIENTA: _x000D_
-Objetivo a superar_x000D_
-Impacto (medible para el cliente) _x000D_
-Decisión_x000D_
-Explicacion Decisión_x000D_
-Acción _x000D_
-Explicacion Acción_x000D_
-Herramienta_x000D_
-Explicacion Herramienta_x000D_
-_x000D_
-(crear el artefacto en base a la herramienta que permita llevar a cabo la acción y por tanto la decisión) _x000D_
-Parte 3:  Resultado_x000D_
-Cada síntoma muestra: semáforo (rojo/ámbar/verde), KPI actual vs. objetivo, y micro‑copy de frases._x000D_
-Usuario puede ordenar, crear, eliminar, etc.... La herramienta es dinámica. _x000D_
-Botón “Generar informe PDF” con todo esto empaquetado._x000D_
-_x000D_
-como sigue: _x000D_
-## 1. Campos que sí forman parte del modelo PIE_x000D_
-Tomando tu Excel (cuadro clinico) como referencia, para **cada síntoma** el artefacto puede quedarse con:_x000D_
-_x000D_
-```json_x000D_
-{_x000D_
-  código/id": "UCI-S1",                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "especialidad": "UCI FINANCIERA",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "departamento": "FINANZAS"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "sintoma": "Hemorragia de Caja",  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "logica_masesora": "Sabemos que tu negocio tiene dinero bloqueado...", // Lógica Asesora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "input_a_": "Stock sin vender &gt;6 meses + facturas &gt;90 días + anticipos sin materializar (€)", // Input A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "input_b_": "Gastos fijos mensuales totales (€)",                                                // Input B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "formula": "(Input A) ÷ (Input B)",                                                            // Fórmula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "resultado": "Meses de dinero atrapado",                                                        // Resultado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "impacto": "Por cada medio mes de dinero que rescatas...",                                    // Impacto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "objetivo_kpi": 0.3,                                                                                  // Objetivo KPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "ejemplo_owner": "Tienes 8.500€ atrapados y 12.000€/mes de gastos = 0,71 meses bloqueados.",         // Ejemplo relleno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "decision": "Localizar el Dinero Invisible",                                                          // Decisión (Optimizador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_decision": "Antes de pedir un crédito...",                                              // Explicación decisión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "accion": "Protocolo de Rescate en 30 Días",                                                         // Acción ACI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_accion": "Identificar 3–5 movimientos concretos...",                                    // Explicación Acción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "herramienta": "Detector de Dinero Invisible",                                                       // Herramienta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_herramienta": "Escanea tus números y te dice...",                                       // Explicación herramienta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "impacto_tratamiento": "Si pasas de 1,2 meses a 0,4, liberas 9.600€...",                             // Impacto tratamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "ejemplo_negocio_real": "Taller mecánico 35k€/mes: 8.500€ atrapados..."                              // Ejemplo negocio real</t>
-  </si>
-  <si>
-    <t>}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTOS CAMPOS SON PARA LA VERSION 2.0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "decision_maestra": "Control Anticipativo de Liquidez",                                              // Decisión Maestra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_decision_maestra": "Pasas de reaccionar cuando falta dinero...",                        // Explicación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "accion_maestra": "Proyectar escenarios de caja a 3 meses",                                          // Acción ACI (maestra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_accion_maestra": "Simulas cobros y pagos futuros...",                                   // Explicación acción maestra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "herramienta_maestra": "Proyector de Caja 90 Días",                                                  // Herramienta maestra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "explicacion_herramienta_maestra": "Como un pronóstico del tiempo de tu dinero...",                  // Explicación</t>
-  </si>
-  <si>
-    <t>- Todo lo de **umbrales, colores, órdenes, estados** se puede resolver en el front/back con reglas fijas: por ejemplo, rojo si `resultado &gt; objetivo_kpi`, ámbar si está cerca, verde si lo cumple.[2]</t>
-  </si>
-  <si>
-    <t>- Las pantallas de “resultado” solo leen `resultado_label`, el valor calculado en runtime y `objetivo_kpi` para pintar el semáforo y el micro‑copy.[3]</t>
-  </si>
-  <si>
-    <t>## 2. Cómo encaja esto con tus pasos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **Paso 1 – Wizard de Síntomas**  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Usa: `logica_masesora`, `input_a`, `input_b`, `formula`, `resultado`, `objetivo`, `ejemplo`.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - El motor solo guarda los números de Input A/B para cada síntoma en memoria/sesión, calcula el KPI y no necesita más campos estructurales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **Paso 2 – Wizard de Herramienta**  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Usa: `objetivo_superar`, `impacto_medible`, `decision`, `explicacion_decision`, `accion`, `explicacion_accion`, `herramienta`, `explicacion_herramienta`, más el bloque “maestro” si queréis mostrarlo ya o solo en el PDF.[1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **Paso 3 – Resultado**  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Para cada síntoma: muestra `nombre_sintoma`, KPI calculado, `objetivo_kpi` y un micro‑copy que se puede montar concatenando el valor calculado + objetivo.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - La lógica de colores y de orden vive en código, no como campos guardados.</t>
-  </si>
-  <si>
-    <t>## 3. Botón “Guardar / Generar PDF”</t>
-  </si>
-  <si>
-    <t>Técnicamente, el “botón guardar PDF” necesita:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Recoger en el front:  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Síntomas que se han usado en el PIE de esa sesión (por ejemplo, UCI‑S1, S2, S3).  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Inputs A/B que introdujo el dueño y el KPI resultante de cada uno.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Opcionalmente, checkbox “he aplicado la herramienta” por síntoma.</t>
-  </si>
-  <si>
-    <t>- Enviar al backend un objeto tipo:</t>
-  </si>
-  <si>
-    <t>```json</t>
-  </si>
-  <si>
-    <t>{</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "empresa": "Nombre / identificador",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "sintomas": [</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "id": "UCI-S1",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "kpi_resultado": 0.71,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "objetivo_kpi": 0.3,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "inputs": { "input_a": 8500, "input_b": 12000 },</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "herramienta_aplicada": true</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    },</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "id": "UCI-S2",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "kpi_resultado": 82,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "objetivo_kpi": 50,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      "herramienta_aplicada": false</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- El backend:  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Lee los metadatos de cada síntoma desde el JSON “maestro” (el modelo que acabamos de definir).[1]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Genera el PDF con: Lógica Masesora, KPIs, decisiones, acciones y herramientas de esos síntomas.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Puede enviarte una copia por mail o guardarlo en tu CRM para que sepas que ese dueño ha terminado el PIE de UCI Financiera.[3]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">la clinica de empresas, con 10 especialidades (departamentos) , con 10 sintomas cada una, el Plan PIE, Plan de Impulso Empresarial que es mi MVP y quiero construir los 10 Pies. </t>
-  </si>
-  <si>
-    <t>YA HEMOS MEJORADO LA ESTRUCTURA DEL PRE, MI DUDA ES NECESITO CREAR LAS 7 HERRAMIENTAS UNIVERSALES, PARA NO HACER CADA SINTOMA DE UNO EN UNO, CORRECTO?</t>
   </si>
 </sst>
 </file>
@@ -12405,7 +11579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -12514,9 +11688,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -13050,1496 +12221,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D70BCCA-9449-43AE-AEC6-B6A814DF80EF}">
-  <dimension ref="A1:A441"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>3243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>3244</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>3245</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>3246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>3247</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>3248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>3249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>3251</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>3252</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>3253</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>3254</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>3255</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>3256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>3257</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>3258</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>3259</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>3260</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>3261</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>3262</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>3263</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>3264</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>3265</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>3266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>3267</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>3268</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>3269</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>3270</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>3271</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>3272</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>3273</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>3274</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>3275</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>3276</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>3277</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>3278</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>3279</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>3280</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>3249</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>3281</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>3282</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>3283</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>3258</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>3284</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>3285</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>3276</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>3277</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>3278</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>3287</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>3289</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>3290</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>3291</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>3292</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>3293</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>3294</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>3295</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>3296</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>3297</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>3298</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>3299</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>3301</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>3302</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>3303</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>3304</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>3305</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>3306</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>3307</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>3308</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>3309</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>3310</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>3311</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>3312</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>3313</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>3314</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>3315</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>3316</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>3317</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>3318</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>3319</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>3320</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" t="s">
-        <v>3321</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>3322</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>3430</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>3426</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>3427</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>3429</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>3428</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>3323</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" t="s">
-        <v>3324</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" t="s">
-        <v>3325</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>3326</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" t="s">
-        <v>3327</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" t="s">
-        <v>3328</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>3329</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>3331</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>3332</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" t="s">
-        <v>3333</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" t="s">
-        <v>3334</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>3335</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" t="s">
-        <v>3336</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>3337</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" t="s">
-        <v>3338</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" t="s">
-        <v>3340</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>3341</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" t="s">
-        <v>3342</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" t="s">
-        <v>3343</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>3344</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>3345</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>3346</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>3347</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>3348</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>3349</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>3350</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>3351</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>3352</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" t="s">
-        <v>3353</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" t="s">
-        <v>3354</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" t="s">
-        <v>3356</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" t="s">
-        <v>3357</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1">
-      <c r="A249" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1">
-      <c r="A250" t="s">
-        <v>3358</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1">
-      <c r="A251" t="s">
-        <v>3359</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" t="s">
-        <v>3360</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1">
-      <c r="A253" t="s">
-        <v>3361</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" t="s">
-        <v>3362</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" t="s">
-        <v>3363</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" t="s">
-        <v>3364</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" t="s">
-        <v>3365</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1">
-      <c r="A260" t="s">
-        <v>3366</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" t="s">
-        <v>3367</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" t="s">
-        <v>3368</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1">
-      <c r="A263" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1">
-      <c r="A264" t="s">
-        <v>3369</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1">
-      <c r="A265" t="s">
-        <v>3370</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1">
-      <c r="A267" t="s">
-        <v>3371</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1">
-      <c r="A268" t="s">
-        <v>3372</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1">
-      <c r="A269" t="s">
-        <v>3373</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" t="s">
-        <v>3374</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" t="s">
-        <v>3375</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" t="s">
-        <v>3376</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" t="s">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1">
-      <c r="A275" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1">
-      <c r="A276" t="s">
-        <v>3378</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1">
-      <c r="A277" t="s">
-        <v>3379</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1">
-      <c r="A278" t="s">
-        <v>3380</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1">
-      <c r="A279" t="s">
-        <v>3381</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1">
-      <c r="A280" t="s">
-        <v>3382</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1">
-      <c r="A282" t="s">
-        <v>3383</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1">
-      <c r="A283" t="s">
-        <v>3384</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1">
-      <c r="A284" t="s">
-        <v>3339</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1">
-      <c r="A285" t="s">
-        <v>3385</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1">
-      <c r="A286" t="s">
-        <v>3386</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1">
-      <c r="A287" t="s">
-        <v>3387</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1">
-      <c r="A288" t="s">
-        <v>3388</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1">
-      <c r="A289" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1">
-      <c r="A290" t="s">
-        <v>3389</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1">
-      <c r="A291" t="s">
-        <v>3390</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1">
-      <c r="A292" t="s">
-        <v>3391</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1">
-      <c r="A293" t="s">
-        <v>3392</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1">
-      <c r="A294" t="s">
-        <v>3393</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1">
-      <c r="A295" t="s">
-        <v>3394</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1">
-      <c r="A296" t="s">
-        <v>3395</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1">
-      <c r="A297" t="s">
-        <v>3396</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1">
-      <c r="A298" t="s">
-        <v>3397</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1">
-      <c r="A300" t="s">
-        <v>3398</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1">
-      <c r="A301" t="s">
-        <v>3346</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1">
-      <c r="A302" t="s">
-        <v>3399</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1">
-      <c r="A303" t="s">
-        <v>3400</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1">
-      <c r="A304" t="s">
-        <v>3401</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1">
-      <c r="A305" t="s">
-        <v>3402</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1">
-      <c r="A306" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1">
-      <c r="A307" t="s">
-        <v>3403</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1">
-      <c r="A308" t="s">
-        <v>3404</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1">
-      <c r="A309" t="s">
-        <v>3405</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1">
-      <c r="A311" t="s">
-        <v>3406</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1">
-      <c r="A312" t="s">
-        <v>3407</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1">
-      <c r="A313" t="s">
-        <v>3408</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1">
-      <c r="A314" t="s">
-        <v>3409</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1">
-      <c r="A315" t="s">
-        <v>3410</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1">
-      <c r="A316" t="s">
-        <v>3411</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1">
-      <c r="A317" t="s">
-        <v>3412</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1">
-      <c r="A318" t="s">
-        <v>3413</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1">
-      <c r="A319" t="s">
-        <v>3414</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1">
-      <c r="A321" t="s">
-        <v>3415</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1">
-      <c r="A322" t="s">
-        <v>3416</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1">
-      <c r="A323" t="s">
-        <v>3417</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1">
-      <c r="A324" t="s">
-        <v>3418</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1">
-      <c r="A325" t="s">
-        <v>3419</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1">
-      <c r="A326" t="s">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1">
-      <c r="A327" t="s">
-        <v>3421</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1">
-      <c r="A328" t="s">
-        <v>3422</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1">
-      <c r="A330" t="s">
-        <v>3423</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1">
-      <c r="A331" t="s">
-        <v>3424</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1">
-      <c r="A332" t="s">
-        <v>3425</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1">
-      <c r="A334" t="s">
-        <v>3502</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1">
-      <c r="A335" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1">
-      <c r="A336" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1">
-      <c r="A337" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1">
-      <c r="A338" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1">
-      <c r="A339" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1">
-      <c r="A340" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1">
-      <c r="A341" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1">
-      <c r="A342" t="s">
-        <v>3242</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1">
-      <c r="A343" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="344" spans="1:1">
-      <c r="A344" t="s">
-        <v>2406</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1">
-      <c r="A345" t="s">
-        <v>3431</v>
-      </c>
-    </row>
-    <row r="346" spans="1:1">
-      <c r="A346" t="s">
-        <v>3432</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1">
-      <c r="A347" t="s">
-        <v>3433</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1">
-      <c r="A348" t="s">
-        <v>3434</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" ht="409.5">
-      <c r="A349" s="39" t="s">
-        <v>3435</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1">
-      <c r="A350" t="s">
-        <v>3436</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1">
-      <c r="A351" t="s">
-        <v>3437</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" t="s">
-        <v>3438</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1">
-      <c r="A354" t="s">
-        <v>3439</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" t="s">
-        <v>3440</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1">
-      <c r="A357" t="s">
-        <v>3441</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1">
-      <c r="A358" t="s">
-        <v>3442</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1">
-      <c r="A359" t="s">
-        <v>3443</v>
-      </c>
-    </row>
-    <row r="360" spans="1:1">
-      <c r="A360" t="s">
-        <v>3444</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1">
-      <c r="A361" t="s">
-        <v>3445</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1">
-      <c r="A363" t="s">
-        <v>3446</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1">
-      <c r="A365" t="s">
-        <v>3447</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1">
-      <c r="A366" t="s">
-        <v>3448</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1">
-      <c r="A367" t="s">
-        <v>3449</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1">
-      <c r="A368" t="s">
-        <v>3450</v>
-      </c>
-    </row>
-    <row r="369" spans="1:1">
-      <c r="A369" t="s">
-        <v>3451</v>
-      </c>
-    </row>
-    <row r="370" spans="1:1">
-      <c r="A370" t="s">
-        <v>3452</v>
-      </c>
-    </row>
-    <row r="372" spans="1:1">
-      <c r="A372" t="s">
-        <v>3453</v>
-      </c>
-    </row>
-    <row r="373" spans="1:1">
-      <c r="A373" t="s">
-        <v>3454</v>
-      </c>
-    </row>
-    <row r="374" spans="1:1">
-      <c r="A374" t="s">
-        <v>3455</v>
-      </c>
-    </row>
-    <row r="375" spans="1:1">
-      <c r="A375" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="376" spans="1:1">
-      <c r="A376" t="s">
-        <v>3456</v>
-      </c>
-    </row>
-    <row r="378" spans="1:1">
-      <c r="A378" t="s">
-        <v>3457</v>
-      </c>
-    </row>
-    <row r="379" spans="1:1">
-      <c r="A379" t="s">
-        <v>3458</v>
-      </c>
-    </row>
-    <row r="380" spans="1:1">
-      <c r="A380" t="s">
-        <v>3459</v>
-      </c>
-    </row>
-    <row r="381" spans="1:1">
-      <c r="A381" t="s">
-        <v>3460</v>
-      </c>
-    </row>
-    <row r="382" spans="1:1">
-      <c r="A382" t="s">
-        <v>3461</v>
-      </c>
-    </row>
-    <row r="383" spans="1:1">
-      <c r="A383" t="s">
-        <v>3462</v>
-      </c>
-    </row>
-    <row r="385" spans="1:1">
-      <c r="A385" t="s">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="387" spans="1:1">
-      <c r="A387" t="s">
-        <v>3463</v>
-      </c>
-    </row>
-    <row r="388" spans="1:1">
-      <c r="A388" t="s">
-        <v>3464</v>
-      </c>
-    </row>
-    <row r="390" spans="1:1">
-      <c r="A390" t="s">
-        <v>3465</v>
-      </c>
-    </row>
-    <row r="392" spans="1:1">
-      <c r="A392" t="s">
-        <v>3466</v>
-      </c>
-    </row>
-    <row r="393" spans="1:1">
-      <c r="A393" t="s">
-        <v>3467</v>
-      </c>
-    </row>
-    <row r="394" spans="1:1">
-      <c r="A394" t="s">
-        <v>3468</v>
-      </c>
-    </row>
-    <row r="396" spans="1:1">
-      <c r="A396" t="s">
-        <v>3469</v>
-      </c>
-    </row>
-    <row r="397" spans="1:1">
-      <c r="A397" t="s">
-        <v>3470</v>
-      </c>
-    </row>
-    <row r="399" spans="1:1">
-      <c r="A399" t="s">
-        <v>3471</v>
-      </c>
-    </row>
-    <row r="400" spans="1:1">
-      <c r="A400" t="s">
-        <v>3472</v>
-      </c>
-    </row>
-    <row r="401" spans="1:1">
-      <c r="A401" t="s">
-        <v>3473</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1">
-      <c r="A403" t="s">
-        <v>3474</v>
-      </c>
-    </row>
-    <row r="405" spans="1:1">
-      <c r="A405" t="s">
-        <v>3475</v>
-      </c>
-    </row>
-    <row r="407" spans="1:1">
-      <c r="A407" t="s">
-        <v>3476</v>
-      </c>
-    </row>
-    <row r="408" spans="1:1">
-      <c r="A408" t="s">
-        <v>3477</v>
-      </c>
-    </row>
-    <row r="409" spans="1:1">
-      <c r="A409" t="s">
-        <v>3478</v>
-      </c>
-    </row>
-    <row r="410" spans="1:1">
-      <c r="A410" t="s">
-        <v>3479</v>
-      </c>
-    </row>
-    <row r="412" spans="1:1">
-      <c r="A412" t="s">
-        <v>3480</v>
-      </c>
-    </row>
-    <row r="414" spans="1:1">
-      <c r="A414" t="s">
-        <v>3481</v>
-      </c>
-    </row>
-    <row r="415" spans="1:1">
-      <c r="A415" t="s">
-        <v>3482</v>
-      </c>
-    </row>
-    <row r="416" spans="1:1">
-      <c r="A416" t="s">
-        <v>3436</v>
-      </c>
-    </row>
-    <row r="417" spans="1:1">
-      <c r="A417" t="s">
-        <v>3483</v>
-      </c>
-    </row>
-    <row r="418" spans="1:1">
-      <c r="A418" t="s">
-        <v>3484</v>
-      </c>
-    </row>
-    <row r="419" spans="1:1">
-      <c r="A419" t="s">
-        <v>3485</v>
-      </c>
-    </row>
-    <row r="420" spans="1:1">
-      <c r="A420" t="s">
-        <v>3486</v>
-      </c>
-    </row>
-    <row r="421" spans="1:1">
-      <c r="A421" t="s">
-        <v>3487</v>
-      </c>
-    </row>
-    <row r="422" spans="1:1">
-      <c r="A422" t="s">
-        <v>3488</v>
-      </c>
-    </row>
-    <row r="423" spans="1:1">
-      <c r="A423" t="s">
-        <v>3489</v>
-      </c>
-    </row>
-    <row r="424" spans="1:1">
-      <c r="A424" t="s">
-        <v>3490</v>
-      </c>
-    </row>
-    <row r="425" spans="1:1">
-      <c r="A425" t="s">
-        <v>3491</v>
-      </c>
-    </row>
-    <row r="426" spans="1:1">
-      <c r="A426" t="s">
-        <v>3485</v>
-      </c>
-    </row>
-    <row r="427" spans="1:1">
-      <c r="A427" t="s">
-        <v>3492</v>
-      </c>
-    </row>
-    <row r="428" spans="1:1">
-      <c r="A428" t="s">
-        <v>3493</v>
-      </c>
-    </row>
-    <row r="429" spans="1:1">
-      <c r="A429" t="s">
-        <v>3494</v>
-      </c>
-    </row>
-    <row r="430" spans="1:1">
-      <c r="A430" t="s">
-        <v>3495</v>
-      </c>
-    </row>
-    <row r="431" spans="1:1">
-      <c r="A431" t="s">
-        <v>3496</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1">
-      <c r="A432" t="s">
-        <v>3497</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1">
-      <c r="A433" t="s">
-        <v>3455</v>
-      </c>
-    </row>
-    <row r="434" spans="1:1">
-      <c r="A434" t="s">
-        <v>3288</v>
-      </c>
-    </row>
-    <row r="436" spans="1:1">
-      <c r="A436" t="s">
-        <v>3498</v>
-      </c>
-    </row>
-    <row r="437" spans="1:1">
-      <c r="A437" t="s">
-        <v>3499</v>
-      </c>
-    </row>
-    <row r="438" spans="1:1">
-      <c r="A438" t="s">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="439" spans="1:1">
-      <c r="A439" t="s">
-        <v>3501</v>
-      </c>
-    </row>
-    <row r="441" spans="1:1">
-      <c r="A441" t="s">
-        <v>3503</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F0DC79-0EAD-4F15-8EFE-C2118F2AA56A}">
   <sheetPr codeName="Hoja1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -15655,7 +13336,7 @@
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
     </row>
-    <row r="24" spans="1:24" ht="179.25" thickBot="1">
+    <row r="24" spans="1:24" ht="166.5" thickBot="1">
       <c r="A24" s="5" t="s">
         <v>432</v>
       </c>
@@ -15703,7 +13384,7 @@
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
     </row>
-    <row r="25" spans="1:24" ht="179.25" thickBot="1">
+    <row r="25" spans="1:24" ht="166.5" thickBot="1">
       <c r="A25" s="5" t="s">
         <v>432</v>
       </c>
@@ -38562,7 +36243,7 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1025" r:id="rId3" name="Control 1">
+        <control shapeId="1029" r:id="rId3" name="Control 5">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -38582,12 +36263,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1025" r:id="rId3" name="Control 1"/>
+        <control shapeId="1029" r:id="rId3" name="Control 5"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1026" r:id="rId5" name="Control 2">
+        <control shapeId="1028" r:id="rId5" name="Control 4">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -38607,7 +36288,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1026" r:id="rId5" name="Control 2"/>
+        <control shapeId="1028" r:id="rId5" name="Control 4"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -38637,7 +36318,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1028" r:id="rId7" name="Control 4">
+        <control shapeId="1026" r:id="rId7" name="Control 2">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -38657,12 +36338,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1028" r:id="rId7" name="Control 4"/>
+        <control shapeId="1026" r:id="rId7" name="Control 2"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1029" r:id="rId8" name="Control 5">
+        <control shapeId="1025" r:id="rId8" name="Control 1">
           <controlPr defaultSize="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
@@ -38682,14 +36363,14 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1029" r:id="rId8" name="Control 5"/>
+        <control shapeId="1025" r:id="rId8" name="Control 1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454BCDA7-81EF-40B7-A67C-DF5428A6F5AD}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
@@ -39055,7 +36736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FC3208-F882-402F-B401-FE156A2FE307}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AD108"/>
@@ -39161,13 +36842,13 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="43" t="s">
         <v>510</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>646</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="43" t="s">
         <v>635</v>
       </c>
       <c r="D2" s="19">
@@ -39251,9 +36932,9 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
       <c r="D3" s="19">
         <v>2</v>
       </c>
@@ -39335,9 +37016,9 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
       <c r="D4" s="19">
         <v>3</v>
       </c>
@@ -39419,9 +37100,9 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="19">
         <v>4</v>
       </c>
@@ -39503,9 +37184,9 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
       <c r="D6" s="19">
         <v>5</v>
       </c>
@@ -39587,9 +37268,9 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="19">
         <v>6</v>
       </c>
@@ -39671,9 +37352,9 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="19">
         <v>7</v>
       </c>
@@ -39755,9 +37436,9 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
       <c r="D9" s="19">
         <v>8</v>
       </c>
@@ -39839,9 +37520,9 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
       <c r="D10" s="19">
         <v>9</v>
       </c>
@@ -39923,9 +37604,9 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
       <c r="D11" s="19">
         <v>10</v>
       </c>
@@ -40007,13 +37688,13 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="43" t="s">
         <v>509</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="43" t="s">
         <v>645</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="43" t="s">
         <v>634</v>
       </c>
       <c r="D12" s="19">
@@ -40097,9 +37778,9 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
       <c r="D13" s="19">
         <v>12</v>
       </c>
@@ -40181,9 +37862,9 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
       <c r="D14" s="19">
         <v>13</v>
       </c>
@@ -40265,9 +37946,9 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
       <c r="D15" s="19">
         <v>14</v>
       </c>
@@ -40349,9 +38030,9 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="19">
         <v>15</v>
       </c>
@@ -40433,9 +38114,9 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
       <c r="D17" s="19">
         <v>16</v>
       </c>
@@ -40517,9 +38198,9 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="19">
         <v>17</v>
       </c>
@@ -40601,9 +38282,9 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
       <c r="D19" s="19">
         <v>18</v>
       </c>
@@ -40685,9 +38366,9 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="19">
         <v>19</v>
       </c>
@@ -40769,9 +38450,9 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
       <c r="D21" s="19">
         <v>20</v>
       </c>
@@ -40853,13 +38534,13 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="43" t="s">
         <v>508</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="43" t="s">
         <v>644</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="43" t="s">
         <v>1071</v>
       </c>
       <c r="D22" s="19">
@@ -40943,9 +38624,9 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
       <c r="D23" s="19">
         <v>22</v>
       </c>
@@ -41027,9 +38708,9 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
       <c r="D24" s="19">
         <v>23</v>
       </c>
@@ -41111,9 +38792,9 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
       <c r="D25" s="19">
         <v>24</v>
       </c>
@@ -41195,9 +38876,9 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
       <c r="D26" s="19">
         <v>25</v>
       </c>
@@ -41279,9 +38960,9 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
       <c r="D27" s="19">
         <v>26</v>
       </c>
@@ -41363,9 +39044,9 @@
       </c>
     </row>
     <row r="28" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="19">
         <v>27</v>
       </c>
@@ -41447,9 +39128,9 @@
       </c>
     </row>
     <row r="29" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
       <c r="D29" s="19">
         <v>28</v>
       </c>
@@ -41531,9 +39212,9 @@
       </c>
     </row>
     <row r="30" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="19">
         <v>29</v>
       </c>
@@ -41615,9 +39296,9 @@
       </c>
     </row>
     <row r="31" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
       <c r="D31" s="19">
         <v>30</v>
       </c>
@@ -41699,13 +39380,13 @@
       </c>
     </row>
     <row r="32" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="43" t="s">
         <v>507</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="43" t="s">
         <v>643</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="43" t="s">
         <v>632</v>
       </c>
       <c r="D32" s="19">
@@ -41789,9 +39470,9 @@
       </c>
     </row>
     <row r="33" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A33" s="45"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
+      <c r="A33" s="44"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
       <c r="D33" s="19">
         <v>32</v>
       </c>
@@ -41873,9 +39554,9 @@
       </c>
     </row>
     <row r="34" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A34" s="45"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
       <c r="D34" s="19">
         <v>33</v>
       </c>
@@ -41957,9 +39638,9 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A35" s="45"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
+      <c r="A35" s="44"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="19">
         <v>34</v>
       </c>
@@ -42041,9 +39722,9 @@
       </c>
     </row>
     <row r="36" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
+      <c r="A36" s="44"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="19">
         <v>35</v>
       </c>
@@ -42125,9 +39806,9 @@
       </c>
     </row>
     <row r="37" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A37" s="45"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
       <c r="D37" s="19">
         <v>36</v>
       </c>
@@ -42209,9 +39890,9 @@
       </c>
     </row>
     <row r="38" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A38" s="45"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
       <c r="D38" s="19">
         <v>37</v>
       </c>
@@ -42293,9 +39974,9 @@
       </c>
     </row>
     <row r="39" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A39" s="45"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
       <c r="D39" s="19">
         <v>38</v>
       </c>
@@ -42377,9 +40058,9 @@
       </c>
     </row>
     <row r="40" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A40" s="45"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
       <c r="D40" s="19">
         <v>39</v>
       </c>
@@ -42461,9 +40142,9 @@
       </c>
     </row>
     <row r="41" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A41" s="46"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
       <c r="D41" s="19">
         <v>40</v>
       </c>
@@ -42545,13 +40226,13 @@
       </c>
     </row>
     <row r="42" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="43" t="s">
         <v>648</v>
       </c>
-      <c r="B42" s="44" t="s">
+      <c r="B42" s="43" t="s">
         <v>642</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="43" t="s">
         <v>631</v>
       </c>
       <c r="D42" s="19">
@@ -42635,9 +40316,9 @@
       </c>
     </row>
     <row r="43" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A43" s="45"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
       <c r="D43" s="19">
         <v>42</v>
       </c>
@@ -42719,9 +40400,9 @@
       </c>
     </row>
     <row r="44" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A44" s="45"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
       <c r="D44" s="19">
         <v>43</v>
       </c>
@@ -42803,9 +40484,9 @@
       </c>
     </row>
     <row r="45" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A45" s="45"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
       <c r="D45" s="19">
         <v>44</v>
       </c>
@@ -42887,9 +40568,9 @@
       </c>
     </row>
     <row r="46" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A46" s="45"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
       <c r="D46" s="19">
         <v>45</v>
       </c>
@@ -42971,9 +40652,9 @@
       </c>
     </row>
     <row r="47" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A47" s="45"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
       <c r="D47" s="19">
         <v>46</v>
       </c>
@@ -43055,9 +40736,9 @@
       </c>
     </row>
     <row r="48" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A48" s="45"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
       <c r="D48" s="19">
         <v>47</v>
       </c>
@@ -43139,9 +40820,9 @@
       </c>
     </row>
     <row r="49" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A49" s="45"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
       <c r="D49" s="19">
         <v>48</v>
       </c>
@@ -43223,9 +40904,9 @@
       </c>
     </row>
     <row r="50" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A50" s="45"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
       <c r="D50" s="19">
         <v>49</v>
       </c>
@@ -43307,9 +40988,9 @@
       </c>
     </row>
     <row r="51" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A51" s="46"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
+      <c r="A51" s="45"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
       <c r="D51" s="19">
         <v>50</v>
       </c>
@@ -43391,13 +41072,13 @@
       </c>
     </row>
     <row r="52" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A52" s="44" t="s">
+      <c r="A52" s="43" t="s">
         <v>505</v>
       </c>
-      <c r="B52" s="44" t="s">
+      <c r="B52" s="43" t="s">
         <v>641</v>
       </c>
-      <c r="C52" s="44" t="s">
+      <c r="C52" s="43" t="s">
         <v>630</v>
       </c>
       <c r="D52" s="19">
@@ -43481,9 +41162,9 @@
       </c>
     </row>
     <row r="53" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A53" s="45"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
+      <c r="A53" s="44"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
       <c r="D53" s="19">
         <v>52</v>
       </c>
@@ -43565,9 +41246,9 @@
       </c>
     </row>
     <row r="54" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A54" s="45"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
+      <c r="A54" s="44"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
       <c r="D54" s="19">
         <v>53</v>
       </c>
@@ -43649,9 +41330,9 @@
       </c>
     </row>
     <row r="55" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A55" s="45"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
+      <c r="A55" s="44"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
       <c r="D55" s="19">
         <v>54</v>
       </c>
@@ -43733,9 +41414,9 @@
       </c>
     </row>
     <row r="56" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A56" s="45"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
+      <c r="A56" s="44"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
       <c r="D56" s="19">
         <v>55</v>
       </c>
@@ -43817,9 +41498,9 @@
       </c>
     </row>
     <row r="57" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A57" s="45"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
+      <c r="A57" s="44"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
       <c r="D57" s="19">
         <v>56</v>
       </c>
@@ -43901,9 +41582,9 @@
       </c>
     </row>
     <row r="58" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A58" s="45"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
+      <c r="A58" s="44"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
       <c r="D58" s="19">
         <v>57</v>
       </c>
@@ -43985,9 +41666,9 @@
       </c>
     </row>
     <row r="59" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A59" s="45"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
+      <c r="A59" s="44"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
       <c r="D59" s="19">
         <v>58</v>
       </c>
@@ -44069,9 +41750,9 @@
       </c>
     </row>
     <row r="60" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A60" s="45"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
+      <c r="A60" s="44"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
       <c r="D60" s="19">
         <v>59</v>
       </c>
@@ -44153,9 +41834,9 @@
       </c>
     </row>
     <row r="61" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A61" s="46"/>
-      <c r="B61" s="46"/>
-      <c r="C61" s="46"/>
+      <c r="A61" s="45"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="45"/>
       <c r="D61" s="19">
         <v>60</v>
       </c>
@@ -44237,13 +41918,13 @@
       </c>
     </row>
     <row r="62" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A62" s="44" t="s">
+      <c r="A62" s="43" t="s">
         <v>504</v>
       </c>
-      <c r="B62" s="44" t="s">
+      <c r="B62" s="43" t="s">
         <v>640</v>
       </c>
-      <c r="C62" s="44" t="s">
+      <c r="C62" s="43" t="s">
         <v>629</v>
       </c>
       <c r="D62" s="19">
@@ -44327,9 +42008,9 @@
       </c>
     </row>
     <row r="63" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A63" s="45"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
+      <c r="A63" s="44"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
       <c r="D63" s="19">
         <v>62</v>
       </c>
@@ -44411,9 +42092,9 @@
       </c>
     </row>
     <row r="64" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A64" s="45"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
+      <c r="A64" s="44"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
       <c r="D64" s="19">
         <v>63</v>
       </c>
@@ -44495,9 +42176,9 @@
       </c>
     </row>
     <row r="65" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A65" s="45"/>
-      <c r="B65" s="45"/>
-      <c r="C65" s="45"/>
+      <c r="A65" s="44"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
       <c r="D65" s="19">
         <v>64</v>
       </c>
@@ -44579,9 +42260,9 @@
       </c>
     </row>
     <row r="66" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A66" s="45"/>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
+      <c r="A66" s="44"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="44"/>
       <c r="D66" s="19">
         <v>65</v>
       </c>
@@ -44663,9 +42344,9 @@
       </c>
     </row>
     <row r="67" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A67" s="45"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
+      <c r="A67" s="44"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
       <c r="D67" s="19">
         <v>66</v>
       </c>
@@ -44747,9 +42428,9 @@
       </c>
     </row>
     <row r="68" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A68" s="45"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
+      <c r="A68" s="44"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
       <c r="D68" s="19">
         <v>67</v>
       </c>
@@ -44831,9 +42512,9 @@
       </c>
     </row>
     <row r="69" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A69" s="45"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
+      <c r="A69" s="44"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
       <c r="D69" s="19">
         <v>68</v>
       </c>
@@ -44915,9 +42596,9 @@
       </c>
     </row>
     <row r="70" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
+      <c r="A70" s="44"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
       <c r="D70" s="19">
         <v>69</v>
       </c>
@@ -44999,9 +42680,9 @@
       </c>
     </row>
     <row r="71" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
+      <c r="A71" s="45"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
       <c r="D71" s="19">
         <v>70</v>
       </c>
@@ -45083,13 +42764,13 @@
       </c>
     </row>
     <row r="72" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A72" s="44" t="s">
+      <c r="A72" s="43" t="s">
         <v>2037</v>
       </c>
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="43" t="s">
         <v>639</v>
       </c>
-      <c r="C72" s="44" t="s">
+      <c r="C72" s="43" t="s">
         <v>628</v>
       </c>
       <c r="D72" s="19">
@@ -45173,9 +42854,9 @@
       </c>
     </row>
     <row r="73" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A73" s="45"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="45"/>
+      <c r="A73" s="44"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="44"/>
       <c r="D73" s="19">
         <v>72</v>
       </c>
@@ -45257,9 +42938,9 @@
       </c>
     </row>
     <row r="74" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A74" s="45"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
+      <c r="A74" s="44"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="44"/>
       <c r="D74" s="19">
         <v>73</v>
       </c>
@@ -45341,9 +43022,9 @@
       </c>
     </row>
     <row r="75" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A75" s="45"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
+      <c r="A75" s="44"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="44"/>
       <c r="D75" s="19">
         <v>74</v>
       </c>
@@ -45425,9 +43106,9 @@
       </c>
     </row>
     <row r="76" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A76" s="45"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
+      <c r="A76" s="44"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
       <c r="D76" s="19">
         <v>75</v>
       </c>
@@ -45509,9 +43190,9 @@
       </c>
     </row>
     <row r="77" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A77" s="45"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
+      <c r="A77" s="44"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
       <c r="D77" s="19">
         <v>76</v>
       </c>
@@ -45593,9 +43274,9 @@
       </c>
     </row>
     <row r="78" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A78" s="45"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
+      <c r="A78" s="44"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="44"/>
       <c r="D78" s="19">
         <v>77</v>
       </c>
@@ -45677,9 +43358,9 @@
       </c>
     </row>
     <row r="79" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A79" s="45"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
+      <c r="A79" s="44"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
       <c r="D79" s="19">
         <v>78</v>
       </c>
@@ -45761,9 +43442,9 @@
       </c>
     </row>
     <row r="80" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A80" s="45"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
+      <c r="A80" s="44"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
       <c r="D80" s="19">
         <v>79</v>
       </c>
@@ -45845,9 +43526,9 @@
       </c>
     </row>
     <row r="81" spans="1:30" ht="49.5" hidden="1" customHeight="1">
-      <c r="A81" s="46"/>
-      <c r="B81" s="46"/>
-      <c r="C81" s="46"/>
+      <c r="A81" s="45"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
       <c r="D81" s="19">
         <v>80</v>
       </c>
@@ -45929,13 +43610,13 @@
       </c>
     </row>
     <row r="82" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A82" s="44" t="s">
+      <c r="A82" s="43" t="s">
         <v>503</v>
       </c>
-      <c r="B82" s="44" t="s">
+      <c r="B82" s="43" t="s">
         <v>638</v>
       </c>
-      <c r="C82" s="44" t="s">
+      <c r="C82" s="43" t="s">
         <v>627</v>
       </c>
       <c r="D82" s="19">
@@ -46019,9 +43700,9 @@
       </c>
     </row>
     <row r="83" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A83" s="45"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
+      <c r="A83" s="44"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="44"/>
       <c r="D83" s="19">
         <v>82</v>
       </c>
@@ -46103,9 +43784,9 @@
       </c>
     </row>
     <row r="84" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A84" s="45"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="45"/>
+      <c r="A84" s="44"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
       <c r="D84" s="19">
         <v>83</v>
       </c>
@@ -46187,9 +43868,9 @@
       </c>
     </row>
     <row r="85" spans="1:30" ht="30" hidden="1" customHeight="1">
-      <c r="A85" s="45"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
+      <c r="A85" s="44"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
       <c r="D85" s="19">
         <v>84</v>
       </c>
@@ -46271,9 +43952,9 @@
       </c>
     </row>
     <row r="86" spans="1:30" ht="30" hidden="1" customHeight="1">
-      <c r="A86" s="45"/>
-      <c r="B86" s="45"/>
-      <c r="C86" s="45"/>
+      <c r="A86" s="44"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
       <c r="D86" s="19">
         <v>85</v>
       </c>
@@ -46355,9 +44036,9 @@
       </c>
     </row>
     <row r="87" spans="1:30" ht="30" hidden="1" customHeight="1">
-      <c r="A87" s="45"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
+      <c r="A87" s="44"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="44"/>
       <c r="D87" s="19">
         <v>86</v>
       </c>
@@ -46439,9 +44120,9 @@
       </c>
     </row>
     <row r="88" spans="1:30" ht="30" hidden="1" customHeight="1">
-      <c r="A88" s="45"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="45"/>
+      <c r="A88" s="44"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="44"/>
       <c r="D88" s="19">
         <v>87</v>
       </c>
@@ -46523,9 +44204,9 @@
       </c>
     </row>
     <row r="89" spans="1:30" ht="30" hidden="1" customHeight="1">
-      <c r="A89" s="45"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
+      <c r="A89" s="44"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="44"/>
       <c r="D89" s="19">
         <v>88</v>
       </c>
@@ -46607,9 +44288,9 @@
       </c>
     </row>
     <row r="90" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A90" s="45"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
+      <c r="A90" s="44"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
       <c r="D90" s="19">
         <v>89</v>
       </c>
@@ -46691,9 +44372,9 @@
       </c>
     </row>
     <row r="91" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A91" s="46"/>
-      <c r="B91" s="46"/>
-      <c r="C91" s="46"/>
+      <c r="A91" s="45"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
       <c r="D91" s="19">
         <v>90</v>
       </c>
@@ -46775,13 +44456,13 @@
       </c>
     </row>
     <row r="92" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A92" s="47" t="s">
+      <c r="A92" s="46" t="s">
         <v>2406</v>
       </c>
-      <c r="B92" s="50" t="s">
+      <c r="B92" s="49" t="s">
         <v>2407</v>
       </c>
-      <c r="C92" s="53" t="s">
+      <c r="C92" s="52" t="s">
         <v>2408</v>
       </c>
       <c r="D92" s="19">
@@ -46865,9 +44546,9 @@
       </c>
     </row>
     <row r="93" spans="1:30" ht="49.5" customHeight="1">
-      <c r="A93" s="48"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="53"/>
+      <c r="A93" s="47"/>
+      <c r="B93" s="50"/>
+      <c r="C93" s="52"/>
       <c r="D93" s="19">
         <v>92</v>
       </c>
@@ -46949,9 +44630,9 @@
       </c>
     </row>
     <row r="94" spans="1:30" ht="55.5" customHeight="1">
-      <c r="A94" s="48"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="53"/>
+      <c r="A94" s="47"/>
+      <c r="B94" s="50"/>
+      <c r="C94" s="52"/>
       <c r="D94" s="19">
         <v>93</v>
       </c>
@@ -47033,9 +44714,9 @@
       </c>
     </row>
     <row r="95" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A95" s="48"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="53"/>
+      <c r="A95" s="47"/>
+      <c r="B95" s="50"/>
+      <c r="C95" s="52"/>
       <c r="D95" s="19">
         <v>94</v>
       </c>
@@ -47117,9 +44798,9 @@
       </c>
     </row>
     <row r="96" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A96" s="48"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="53"/>
+      <c r="A96" s="47"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="52"/>
       <c r="D96" s="19">
         <v>95</v>
       </c>
@@ -47201,9 +44882,9 @@
       </c>
     </row>
     <row r="97" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A97" s="48"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="53"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="52"/>
       <c r="D97" s="19">
         <v>96</v>
       </c>
@@ -47285,9 +44966,9 @@
       </c>
     </row>
     <row r="98" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A98" s="48"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="53"/>
+      <c r="A98" s="47"/>
+      <c r="B98" s="50"/>
+      <c r="C98" s="52"/>
       <c r="D98" s="19">
         <v>97</v>
       </c>
@@ -47369,9 +45050,9 @@
       </c>
     </row>
     <row r="99" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A99" s="48"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="53"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="52"/>
       <c r="D99" s="19">
         <v>98</v>
       </c>
@@ -47453,9 +45134,9 @@
       </c>
     </row>
     <row r="100" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A100" s="48"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="53"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="52"/>
       <c r="D100" s="19">
         <v>99</v>
       </c>
@@ -47537,9 +45218,9 @@
       </c>
     </row>
     <row r="101" spans="1:30" ht="33" hidden="1" customHeight="1">
-      <c r="A101" s="49"/>
-      <c r="B101" s="52"/>
-      <c r="C101" s="53"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="52"/>
       <c r="D101" s="19">
         <v>100</v>
       </c>
@@ -47647,2379 +45328,2379 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="30">
+    <mergeCell ref="A82:A91"/>
+    <mergeCell ref="B82:B91"/>
+    <mergeCell ref="C82:C91"/>
+    <mergeCell ref="A92:A101"/>
+    <mergeCell ref="B92:B101"/>
+    <mergeCell ref="C92:C101"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="B62:B71"/>
+    <mergeCell ref="C62:C71"/>
+    <mergeCell ref="A72:A81"/>
+    <mergeCell ref="B72:B81"/>
+    <mergeCell ref="C72:C81"/>
+    <mergeCell ref="A42:A51"/>
+    <mergeCell ref="B42:B51"/>
+    <mergeCell ref="C42:C51"/>
+    <mergeCell ref="A52:A61"/>
+    <mergeCell ref="B52:B61"/>
+    <mergeCell ref="C52:C61"/>
+    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="B22:B31"/>
+    <mergeCell ref="C22:C31"/>
+    <mergeCell ref="A32:A41"/>
+    <mergeCell ref="B32:B41"/>
+    <mergeCell ref="C32:C41"/>
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="C2:C11"/>
     <mergeCell ref="A12:A21"/>
     <mergeCell ref="B12:B21"/>
     <mergeCell ref="C12:C21"/>
-    <mergeCell ref="A22:A31"/>
-    <mergeCell ref="B22:B31"/>
-    <mergeCell ref="C22:C31"/>
-    <mergeCell ref="A32:A41"/>
-    <mergeCell ref="B32:B41"/>
-    <mergeCell ref="C32:C41"/>
-    <mergeCell ref="A42:A51"/>
-    <mergeCell ref="B42:B51"/>
-    <mergeCell ref="C42:C51"/>
-    <mergeCell ref="A52:A61"/>
-    <mergeCell ref="B52:B61"/>
-    <mergeCell ref="C52:C61"/>
-    <mergeCell ref="A62:A71"/>
-    <mergeCell ref="B62:B71"/>
-    <mergeCell ref="C62:C71"/>
-    <mergeCell ref="A72:A81"/>
-    <mergeCell ref="B72:B81"/>
-    <mergeCell ref="C72:C81"/>
-    <mergeCell ref="A82:A91"/>
-    <mergeCell ref="B82:B91"/>
-    <mergeCell ref="C82:C91"/>
-    <mergeCell ref="A92:A101"/>
-    <mergeCell ref="B92:B101"/>
-    <mergeCell ref="C92:C101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4679C6C-F75D-48A4-A896-82C05C8EFCEA}">
   <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="40" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="40" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="49.140625" style="40" customWidth="1"/>
-    <col min="6" max="6" width="34" style="40" customWidth="1"/>
-    <col min="7" max="7" width="32.42578125" style="40" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="40"/>
-    <col min="9" max="9" width="15.85546875" style="40" customWidth="1"/>
-    <col min="10" max="10" width="44.28515625" style="40" customWidth="1"/>
-    <col min="11" max="16" width="15.85546875" style="40" customWidth="1"/>
-    <col min="17" max="17" width="35" style="40" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="40" customWidth="1"/>
-    <col min="19" max="19" width="35" style="40" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="40"/>
-    <col min="21" max="22" width="35" style="40" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" style="40" customWidth="1"/>
-    <col min="24" max="24" width="11.42578125" style="40"/>
-    <col min="25" max="25" width="41.28515625" style="40" customWidth="1"/>
-    <col min="26" max="26" width="11.42578125" style="40"/>
-    <col min="27" max="27" width="41.28515625" style="40" customWidth="1"/>
-    <col min="28" max="28" width="11.42578125" style="40"/>
-    <col min="29" max="29" width="41.28515625" style="40" customWidth="1"/>
-    <col min="30" max="30" width="119.140625" style="40" customWidth="1"/>
-    <col min="31" max="16384" width="11.42578125" style="40"/>
+    <col min="1" max="1" width="5.5703125" style="39" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="39" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="39" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="39" customWidth="1"/>
+    <col min="5" max="5" width="49.140625" style="39" customWidth="1"/>
+    <col min="6" max="6" width="34" style="39" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" style="39" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="39"/>
+    <col min="9" max="9" width="15.85546875" style="39" customWidth="1"/>
+    <col min="10" max="10" width="44.28515625" style="39" customWidth="1"/>
+    <col min="11" max="16" width="15.85546875" style="39" customWidth="1"/>
+    <col min="17" max="17" width="35" style="39" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" style="39" customWidth="1"/>
+    <col min="19" max="19" width="35" style="39" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" style="39"/>
+    <col min="21" max="22" width="35" style="39" customWidth="1"/>
+    <col min="23" max="23" width="16.140625" style="39" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" style="39"/>
+    <col min="25" max="25" width="41.28515625" style="39" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" style="39"/>
+    <col min="27" max="27" width="41.28515625" style="39" customWidth="1"/>
+    <col min="28" max="28" width="11.42578125" style="39"/>
+    <col min="29" max="29" width="41.28515625" style="39" customWidth="1"/>
+    <col min="30" max="30" width="119.140625" style="39" customWidth="1"/>
+    <col min="31" max="16384" width="11.42578125" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="25.5">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>650</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>651</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>2662</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="39" t="s">
         <v>653</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="39" t="s">
         <v>654</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="J1" s="40" t="s">
+      <c r="J1" s="39" t="s">
         <v>655</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="39" t="s">
         <v>656</v>
       </c>
-      <c r="L1" s="40" t="s">
+      <c r="L1" s="39" t="s">
         <v>657</v>
       </c>
-      <c r="M1" s="40" t="s">
+      <c r="M1" s="39" t="s">
         <v>658</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="39" t="s">
         <v>659</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="P1" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="39" t="s">
         <v>660</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="S1" s="40" t="s">
+      <c r="S1" s="39" t="s">
         <v>661</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="T1" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="U1" s="40" t="s">
+      <c r="U1" s="39" t="s">
         <v>662</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="V1" s="39" t="s">
         <v>2663</v>
       </c>
-      <c r="W1" s="40" t="s">
+      <c r="W1" s="39" t="s">
         <v>2664</v>
       </c>
-      <c r="X1" s="40" t="s">
+      <c r="X1" s="39" t="s">
         <v>663</v>
       </c>
-      <c r="Y1" s="40" t="s">
+      <c r="Y1" s="39" t="s">
         <v>660</v>
       </c>
-      <c r="Z1" s="40" t="s">
+      <c r="Z1" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="AA1" s="40" t="s">
+      <c r="AA1" s="39" t="s">
         <v>661</v>
       </c>
-      <c r="AB1" s="40" t="s">
+      <c r="AB1" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="AC1" s="40" t="s">
+      <c r="AC1" s="39" t="s">
         <v>662</v>
       </c>
-      <c r="AD1" s="40" t="s">
+      <c r="AD1" s="39" t="s">
         <v>2665</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="89.25">
-      <c r="A2" s="40">
+      <c r="A2" s="39">
         <v>1</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>2666</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="39" t="s">
         <v>2667</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="39" t="s">
         <v>2668</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="39" t="s">
         <v>2669</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="39" t="s">
         <v>2670</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="39" t="s">
         <v>2671</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="39" t="s">
         <v>2672</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="39" t="s">
         <v>2673</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="39" t="s">
         <v>2674</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="39" t="s">
         <v>2675</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="39" t="s">
         <v>2676</v>
       </c>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="39" t="s">
         <v>2677</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="R2" s="39" t="s">
         <v>2678</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="S2" s="39" t="s">
         <v>2679</v>
       </c>
-      <c r="T2" s="40" t="s">
+      <c r="T2" s="39" t="s">
         <v>2680</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="39" t="s">
         <v>2681</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="V2" s="39" t="s">
         <v>2682</v>
       </c>
-      <c r="W2" s="40" t="s">
+      <c r="W2" s="39" t="s">
         <v>2683</v>
       </c>
-      <c r="X2" s="40" t="s">
+      <c r="X2" s="39" t="s">
         <v>2684</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Y2" s="39" t="s">
         <v>2685</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="Z2" s="39" t="s">
         <v>2686</v>
       </c>
-      <c r="AA2" s="40" t="s">
+      <c r="AA2" s="39" t="s">
         <v>2687</v>
       </c>
-      <c r="AB2" s="40" t="s">
+      <c r="AB2" s="39" t="s">
         <v>2688</v>
       </c>
-      <c r="AC2" s="40" t="s">
+      <c r="AC2" s="39" t="s">
         <v>2689</v>
       </c>
-      <c r="AD2" s="40" t="s">
+      <c r="AD2" s="39" t="s">
         <v>2690</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="89.25">
-      <c r="A3" s="40">
+      <c r="A3" s="39">
         <v>2</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="39" t="s">
         <v>2691</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="39" t="s">
         <v>2692</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="39" t="s">
         <v>2693</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="39" t="s">
         <v>2694</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="39" t="s">
         <v>2695</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="39" t="s">
         <v>2696</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" s="39" t="s">
         <v>2697</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="39" t="s">
         <v>2698</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="39" t="s">
         <v>2699</v>
       </c>
-      <c r="N3" s="40" t="s">
+      <c r="N3" s="39" t="s">
         <v>2700</v>
       </c>
-      <c r="O3" s="40" t="s">
+      <c r="O3" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="39" t="s">
         <v>2701</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="39" t="s">
         <v>2702</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="39" t="s">
         <v>2703</v>
       </c>
-      <c r="S3" s="40" t="s">
+      <c r="S3" s="39" t="s">
         <v>2704</v>
       </c>
-      <c r="T3" s="40" t="s">
+      <c r="T3" s="39" t="s">
         <v>2705</v>
       </c>
-      <c r="U3" s="40" t="s">
+      <c r="U3" s="39" t="s">
         <v>2706</v>
       </c>
-      <c r="V3" s="40" t="s">
+      <c r="V3" s="39" t="s">
         <v>2707</v>
       </c>
-      <c r="W3" s="40" t="s">
+      <c r="W3" s="39" t="s">
         <v>2708</v>
       </c>
-      <c r="X3" s="40" t="s">
+      <c r="X3" s="39" t="s">
         <v>2709</v>
       </c>
-      <c r="Y3" s="40" t="s">
+      <c r="Y3" s="39" t="s">
         <v>2710</v>
       </c>
-      <c r="Z3" s="40" t="s">
+      <c r="Z3" s="39" t="s">
         <v>2711</v>
       </c>
-      <c r="AA3" s="40" t="s">
+      <c r="AA3" s="39" t="s">
         <v>2712</v>
       </c>
-      <c r="AB3" s="40" t="s">
+      <c r="AB3" s="39" t="s">
         <v>2713</v>
       </c>
-      <c r="AC3" s="40" t="s">
+      <c r="AC3" s="39" t="s">
         <v>2714</v>
       </c>
-      <c r="AD3" s="40" t="s">
+      <c r="AD3" s="39" t="s">
         <v>2715</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="89.25">
-      <c r="A4" s="40">
+      <c r="A4" s="39">
         <v>3</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="39" t="s">
         <v>2716</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="39" t="s">
         <v>2717</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>2718</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="39" t="s">
         <v>2719</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="39" t="s">
         <v>2720</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="39" t="s">
         <v>2721</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="39" t="s">
         <v>2722</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="39" t="s">
         <v>2723</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="39" t="s">
         <v>2724</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="N4" s="39" t="s">
         <v>2725</v>
       </c>
-      <c r="O4" s="40" t="s">
+      <c r="O4" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="P4" s="40" t="s">
+      <c r="P4" s="39" t="s">
         <v>2726</v>
       </c>
-      <c r="Q4" s="40" t="s">
+      <c r="Q4" s="39" t="s">
         <v>2727</v>
       </c>
-      <c r="R4" s="40" t="s">
+      <c r="R4" s="39" t="s">
         <v>2728</v>
       </c>
-      <c r="S4" s="40" t="s">
+      <c r="S4" s="39" t="s">
         <v>2729</v>
       </c>
-      <c r="T4" s="40" t="s">
+      <c r="T4" s="39" t="s">
         <v>2730</v>
       </c>
-      <c r="U4" s="40" t="s">
+      <c r="U4" s="39" t="s">
         <v>2731</v>
       </c>
-      <c r="V4" s="40" t="s">
+      <c r="V4" s="39" t="s">
         <v>2732</v>
       </c>
-      <c r="W4" s="40" t="s">
+      <c r="W4" s="39" t="s">
         <v>2733</v>
       </c>
-      <c r="X4" s="40" t="s">
+      <c r="X4" s="39" t="s">
         <v>2734</v>
       </c>
-      <c r="Y4" s="40" t="s">
+      <c r="Y4" s="39" t="s">
         <v>2735</v>
       </c>
-      <c r="Z4" s="40" t="s">
+      <c r="Z4" s="39" t="s">
         <v>2736</v>
       </c>
-      <c r="AA4" s="40" t="s">
+      <c r="AA4" s="39" t="s">
         <v>2737</v>
       </c>
-      <c r="AB4" s="40" t="s">
+      <c r="AB4" s="39" t="s">
         <v>2738</v>
       </c>
-      <c r="AC4" s="40" t="s">
+      <c r="AC4" s="39" t="s">
         <v>2739</v>
       </c>
-      <c r="AD4" s="40" t="s">
+      <c r="AD4" s="39" t="s">
         <v>2740</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="89.25">
-      <c r="A5" s="40">
+      <c r="A5" s="39">
         <v>11</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="39" t="s">
         <v>2741</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="39" t="s">
         <v>2742</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>2743</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="39" t="s">
         <v>2744</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="39" t="s">
         <v>2745</v>
       </c>
-      <c r="J5" s="40" t="s">
+      <c r="J5" s="39" t="s">
         <v>2746</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="39" t="s">
         <v>2747</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="39" t="s">
         <v>2748</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="39" t="s">
         <v>2749</v>
       </c>
-      <c r="N5" s="40" t="s">
+      <c r="N5" s="39" t="s">
         <v>2750</v>
       </c>
-      <c r="O5" s="40" t="s">
+      <c r="O5" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="P5" s="40" t="s">
+      <c r="P5" s="39" t="s">
         <v>2751</v>
       </c>
-      <c r="Q5" s="40" t="s">
+      <c r="Q5" s="39" t="s">
         <v>2752</v>
       </c>
-      <c r="R5" s="40" t="s">
+      <c r="R5" s="39" t="s">
         <v>2753</v>
       </c>
-      <c r="S5" s="40" t="s">
+      <c r="S5" s="39" t="s">
         <v>2754</v>
       </c>
-      <c r="T5" s="40" t="s">
+      <c r="T5" s="39" t="s">
         <v>2755</v>
       </c>
-      <c r="U5" s="40" t="s">
+      <c r="U5" s="39" t="s">
         <v>2756</v>
       </c>
-      <c r="V5" s="40" t="s">
+      <c r="V5" s="39" t="s">
         <v>2757</v>
       </c>
-      <c r="W5" s="40" t="s">
+      <c r="W5" s="39" t="s">
         <v>2758</v>
       </c>
-      <c r="X5" s="40" t="s">
+      <c r="X5" s="39" t="s">
         <v>2759</v>
       </c>
-      <c r="Y5" s="40" t="s">
+      <c r="Y5" s="39" t="s">
         <v>2760</v>
       </c>
-      <c r="Z5" s="40" t="s">
+      <c r="Z5" s="39" t="s">
         <v>2761</v>
       </c>
-      <c r="AA5" s="40" t="s">
+      <c r="AA5" s="39" t="s">
         <v>2762</v>
       </c>
-      <c r="AB5" s="40" t="s">
+      <c r="AB5" s="39" t="s">
         <v>2763</v>
       </c>
-      <c r="AC5" s="40" t="s">
+      <c r="AC5" s="39" t="s">
         <v>2764</v>
       </c>
-      <c r="AD5" s="40" t="s">
+      <c r="AD5" s="39" t="s">
         <v>2765</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="89.25">
-      <c r="A6" s="40">
+      <c r="A6" s="39">
         <v>12</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="39" t="s">
         <v>2766</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="39" t="s">
         <v>2767</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="39" t="s">
         <v>2768</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="39" t="s">
         <v>2770</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="39" t="s">
         <v>2771</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="39" t="s">
         <v>2772</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="39" t="s">
         <v>2773</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="39" t="s">
         <v>2774</v>
       </c>
-      <c r="N6" s="40" t="s">
+      <c r="N6" s="39" t="s">
         <v>2775</v>
       </c>
-      <c r="O6" s="40" t="s">
+      <c r="O6" s="39" t="s">
         <v>2776</v>
       </c>
-      <c r="P6" s="40" t="s">
+      <c r="P6" s="39" t="s">
         <v>2777</v>
       </c>
-      <c r="Q6" s="40" t="s">
+      <c r="Q6" s="39" t="s">
         <v>2778</v>
       </c>
-      <c r="R6" s="40" t="s">
+      <c r="R6" s="39" t="s">
         <v>2779</v>
       </c>
-      <c r="S6" s="40" t="s">
+      <c r="S6" s="39" t="s">
         <v>2780</v>
       </c>
-      <c r="T6" s="40" t="s">
+      <c r="T6" s="39" t="s">
         <v>2781</v>
       </c>
-      <c r="U6" s="40" t="s">
+      <c r="U6" s="39" t="s">
         <v>2782</v>
       </c>
-      <c r="V6" s="40" t="s">
+      <c r="V6" s="39" t="s">
         <v>2783</v>
       </c>
-      <c r="W6" s="40" t="s">
+      <c r="W6" s="39" t="s">
         <v>2784</v>
       </c>
-      <c r="X6" s="40" t="s">
+      <c r="X6" s="39" t="s">
         <v>2785</v>
       </c>
-      <c r="Y6" s="40" t="s">
+      <c r="Y6" s="39" t="s">
         <v>2786</v>
       </c>
-      <c r="Z6" s="40" t="s">
+      <c r="Z6" s="39" t="s">
         <v>2787</v>
       </c>
-      <c r="AA6" s="40" t="s">
+      <c r="AA6" s="39" t="s">
         <v>2788</v>
       </c>
-      <c r="AB6" s="40" t="s">
+      <c r="AB6" s="39" t="s">
         <v>906</v>
       </c>
-      <c r="AC6" s="40" t="s">
+      <c r="AC6" s="39" t="s">
         <v>2789</v>
       </c>
-      <c r="AD6" s="40" t="s">
+      <c r="AD6" s="39" t="s">
         <v>2790</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="89.25">
-      <c r="A7" s="40">
+      <c r="A7" s="39">
         <v>13</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="39" t="s">
         <v>2791</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="39" t="s">
         <v>2792</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="39" t="s">
         <v>2793</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="39" t="s">
         <v>2794</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="39" t="s">
         <v>2795</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" s="39" t="s">
         <v>2796</v>
       </c>
-      <c r="L7" s="40" t="s">
+      <c r="L7" s="39" t="s">
         <v>2797</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" s="39" t="s">
         <v>2798</v>
       </c>
-      <c r="N7" s="40" t="s">
+      <c r="N7" s="39" t="s">
         <v>2799</v>
       </c>
-      <c r="O7" s="40" t="s">
+      <c r="O7" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="P7" s="40" t="s">
+      <c r="P7" s="39" t="s">
         <v>2800</v>
       </c>
-      <c r="Q7" s="40" t="s">
+      <c r="Q7" s="39" t="s">
         <v>2801</v>
       </c>
-      <c r="R7" s="40" t="s">
+      <c r="R7" s="39" t="s">
         <v>2802</v>
       </c>
-      <c r="S7" s="40" t="s">
+      <c r="S7" s="39" t="s">
         <v>2803</v>
       </c>
-      <c r="T7" s="40" t="s">
+      <c r="T7" s="39" t="s">
         <v>2804</v>
       </c>
-      <c r="U7" s="40" t="s">
+      <c r="U7" s="39" t="s">
         <v>2805</v>
       </c>
-      <c r="V7" s="40" t="s">
+      <c r="V7" s="39" t="s">
         <v>2806</v>
       </c>
-      <c r="W7" s="40" t="s">
+      <c r="W7" s="39" t="s">
         <v>2807</v>
       </c>
-      <c r="X7" s="40" t="s">
+      <c r="X7" s="39" t="s">
         <v>2808</v>
       </c>
-      <c r="Y7" s="40" t="s">
+      <c r="Y7" s="39" t="s">
         <v>2809</v>
       </c>
-      <c r="Z7" s="40" t="s">
+      <c r="Z7" s="39" t="s">
         <v>2810</v>
       </c>
-      <c r="AA7" s="40" t="s">
+      <c r="AA7" s="39" t="s">
         <v>2811</v>
       </c>
-      <c r="AB7" s="40" t="s">
+      <c r="AB7" s="39" t="s">
         <v>2812</v>
       </c>
-      <c r="AC7" s="40" t="s">
+      <c r="AC7" s="39" t="s">
         <v>2813</v>
       </c>
-      <c r="AD7" s="40" t="s">
+      <c r="AD7" s="39" t="s">
         <v>2814</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="89.25">
-      <c r="A8" s="40">
+      <c r="A8" s="39">
         <v>21</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="39" t="s">
         <v>2815</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="39" t="s">
         <v>2816</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>2817</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="39" t="s">
         <v>2818</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="39" t="s">
         <v>2819</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="39" t="s">
         <v>2820</v>
       </c>
-      <c r="L8" s="40" t="s">
+      <c r="L8" s="39" t="s">
         <v>2821</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="39" t="s">
         <v>2822</v>
       </c>
-      <c r="N8" s="40" t="s">
+      <c r="N8" s="39" t="s">
         <v>2823</v>
       </c>
-      <c r="O8" s="40" t="s">
+      <c r="O8" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="P8" s="40" t="s">
+      <c r="P8" s="39" t="s">
         <v>2824</v>
       </c>
-      <c r="Q8" s="40" t="s">
+      <c r="Q8" s="39" t="s">
         <v>2825</v>
       </c>
-      <c r="R8" s="40" t="s">
+      <c r="R8" s="39" t="s">
         <v>2826</v>
       </c>
-      <c r="S8" s="40" t="s">
+      <c r="S8" s="39" t="s">
         <v>2827</v>
       </c>
-      <c r="T8" s="40" t="s">
+      <c r="T8" s="39" t="s">
         <v>2828</v>
       </c>
-      <c r="U8" s="40" t="s">
+      <c r="U8" s="39" t="s">
         <v>2829</v>
       </c>
-      <c r="V8" s="40" t="s">
+      <c r="V8" s="39" t="s">
         <v>2830</v>
       </c>
-      <c r="W8" s="40" t="s">
+      <c r="W8" s="39" t="s">
         <v>2831</v>
       </c>
-      <c r="X8" s="40" t="s">
+      <c r="X8" s="39" t="s">
         <v>2832</v>
       </c>
-      <c r="Y8" s="40" t="s">
+      <c r="Y8" s="39" t="s">
         <v>2833</v>
       </c>
-      <c r="Z8" s="40" t="s">
+      <c r="Z8" s="39" t="s">
         <v>2834</v>
       </c>
-      <c r="AA8" s="40" t="s">
+      <c r="AA8" s="39" t="s">
         <v>2835</v>
       </c>
-      <c r="AB8" s="40" t="s">
+      <c r="AB8" s="39" t="s">
         <v>1091</v>
       </c>
-      <c r="AC8" s="40" t="s">
+      <c r="AC8" s="39" t="s">
         <v>2836</v>
       </c>
-      <c r="AD8" s="40" t="s">
+      <c r="AD8" s="39" t="s">
         <v>2837</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="76.5">
-      <c r="A9" s="40">
+      <c r="A9" s="39">
         <v>22</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="39" t="s">
         <v>2838</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="39" t="s">
         <v>2839</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>2840</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="39" t="s">
         <v>2841</v>
       </c>
-      <c r="J9" s="40" t="s">
+      <c r="J9" s="39" t="s">
         <v>2842</v>
       </c>
-      <c r="K9" s="40" t="s">
+      <c r="K9" s="39" t="s">
         <v>2843</v>
       </c>
-      <c r="L9" s="40" t="s">
+      <c r="L9" s="39" t="s">
         <v>2844</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" s="39" t="s">
         <v>2845</v>
       </c>
-      <c r="N9" s="40" t="s">
+      <c r="N9" s="39" t="s">
         <v>2846</v>
       </c>
-      <c r="O9" s="40" t="s">
+      <c r="O9" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="P9" s="40" t="s">
+      <c r="P9" s="39" t="s">
         <v>2847</v>
       </c>
-      <c r="Q9" s="40" t="s">
+      <c r="Q9" s="39" t="s">
         <v>2848</v>
       </c>
-      <c r="R9" s="40" t="s">
+      <c r="R9" s="39" t="s">
         <v>2849</v>
       </c>
-      <c r="S9" s="40" t="s">
+      <c r="S9" s="39" t="s">
         <v>2850</v>
       </c>
-      <c r="T9" s="40" t="s">
+      <c r="T9" s="39" t="s">
         <v>2851</v>
       </c>
-      <c r="U9" s="40" t="s">
+      <c r="U9" s="39" t="s">
         <v>2852</v>
       </c>
-      <c r="V9" s="40" t="s">
+      <c r="V9" s="39" t="s">
         <v>2853</v>
       </c>
-      <c r="W9" s="40" t="s">
+      <c r="W9" s="39" t="s">
         <v>2854</v>
       </c>
-      <c r="X9" s="40" t="s">
+      <c r="X9" s="39" t="s">
         <v>2855</v>
       </c>
-      <c r="Y9" s="40" t="s">
+      <c r="Y9" s="39" t="s">
         <v>2856</v>
       </c>
-      <c r="Z9" s="40" t="s">
+      <c r="Z9" s="39" t="s">
         <v>2857</v>
       </c>
-      <c r="AA9" s="40" t="s">
+      <c r="AA9" s="39" t="s">
         <v>2858</v>
       </c>
-      <c r="AB9" s="40" t="s">
+      <c r="AB9" s="39" t="s">
         <v>2859</v>
       </c>
-      <c r="AC9" s="40" t="s">
+      <c r="AC9" s="39" t="s">
         <v>2860</v>
       </c>
-      <c r="AD9" s="40" t="s">
+      <c r="AD9" s="39" t="s">
         <v>2861</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="89.25">
-      <c r="A10" s="40">
+      <c r="A10" s="39">
         <v>23</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="39" t="s">
         <v>2862</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="39" t="s">
         <v>2863</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>2864</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="39" t="s">
         <v>2865</v>
       </c>
-      <c r="J10" s="40" t="s">
+      <c r="J10" s="39" t="s">
         <v>2866</v>
       </c>
-      <c r="K10" s="40" t="s">
+      <c r="K10" s="39" t="s">
         <v>2867</v>
       </c>
-      <c r="L10" s="40" t="s">
+      <c r="L10" s="39" t="s">
         <v>2868</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="39" t="s">
         <v>2869</v>
       </c>
-      <c r="N10" s="40" t="s">
+      <c r="N10" s="39" t="s">
         <v>2870</v>
       </c>
-      <c r="O10" s="40" t="s">
+      <c r="O10" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="P10" s="40" t="s">
+      <c r="P10" s="39" t="s">
         <v>2871</v>
       </c>
-      <c r="Q10" s="40" t="s">
+      <c r="Q10" s="39" t="s">
         <v>2872</v>
       </c>
-      <c r="R10" s="40" t="s">
+      <c r="R10" s="39" t="s">
         <v>2873</v>
       </c>
-      <c r="S10" s="40" t="s">
+      <c r="S10" s="39" t="s">
         <v>2874</v>
       </c>
-      <c r="T10" s="40" t="s">
+      <c r="T10" s="39" t="s">
         <v>2875</v>
       </c>
-      <c r="U10" s="40" t="s">
+      <c r="U10" s="39" t="s">
         <v>2876</v>
       </c>
-      <c r="V10" s="40" t="s">
+      <c r="V10" s="39" t="s">
         <v>2877</v>
       </c>
-      <c r="W10" s="40" t="s">
+      <c r="W10" s="39" t="s">
         <v>2878</v>
       </c>
-      <c r="X10" s="40" t="s">
+      <c r="X10" s="39" t="s">
         <v>2879</v>
       </c>
-      <c r="Y10" s="40" t="s">
+      <c r="Y10" s="39" t="s">
         <v>2880</v>
       </c>
-      <c r="Z10" s="40" t="s">
+      <c r="Z10" s="39" t="s">
         <v>2881</v>
       </c>
-      <c r="AA10" s="40" t="s">
+      <c r="AA10" s="39" t="s">
         <v>2882</v>
       </c>
-      <c r="AB10" s="40" t="s">
+      <c r="AB10" s="39" t="s">
         <v>2883</v>
       </c>
-      <c r="AC10" s="40" t="s">
+      <c r="AC10" s="39" t="s">
         <v>2884</v>
       </c>
-      <c r="AD10" s="40" t="s">
+      <c r="AD10" s="39" t="s">
         <v>2885</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="89.25">
-      <c r="A11" s="40">
+      <c r="A11" s="39">
         <v>31</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="39" t="s">
         <v>2886</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="39" t="s">
         <v>2887</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>2888</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" s="39" t="s">
         <v>2889</v>
       </c>
-      <c r="J11" s="40" t="s">
+      <c r="J11" s="39" t="s">
         <v>2890</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="39" t="s">
         <v>2891</v>
       </c>
-      <c r="L11" s="40" t="s">
+      <c r="L11" s="39" t="s">
         <v>2892</v>
       </c>
-      <c r="M11" s="40" t="s">
+      <c r="M11" s="39" t="s">
         <v>2893</v>
       </c>
-      <c r="N11" s="40" t="s">
+      <c r="N11" s="39" t="s">
         <v>2894</v>
       </c>
-      <c r="O11" s="40" t="s">
+      <c r="O11" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="39" t="s">
         <v>2895</v>
       </c>
-      <c r="Q11" s="40" t="s">
+      <c r="Q11" s="39" t="s">
         <v>2896</v>
       </c>
-      <c r="R11" s="40" t="s">
+      <c r="R11" s="39" t="s">
         <v>2897</v>
       </c>
-      <c r="S11" s="40" t="s">
+      <c r="S11" s="39" t="s">
         <v>2898</v>
       </c>
-      <c r="T11" s="40" t="s">
+      <c r="T11" s="39" t="s">
         <v>2899</v>
       </c>
-      <c r="U11" s="40" t="s">
+      <c r="U11" s="39" t="s">
         <v>2900</v>
       </c>
-      <c r="V11" s="40" t="s">
+      <c r="V11" s="39" t="s">
         <v>2901</v>
       </c>
-      <c r="W11" s="40" t="s">
+      <c r="W11" s="39" t="s">
         <v>2902</v>
       </c>
-      <c r="X11" s="40" t="s">
+      <c r="X11" s="39" t="s">
         <v>2903</v>
       </c>
-      <c r="Y11" s="40" t="s">
+      <c r="Y11" s="39" t="s">
         <v>2904</v>
       </c>
-      <c r="Z11" s="40" t="s">
+      <c r="Z11" s="39" t="s">
         <v>2905</v>
       </c>
-      <c r="AA11" s="40" t="s">
+      <c r="AA11" s="39" t="s">
         <v>2906</v>
       </c>
-      <c r="AB11" s="40" t="s">
+      <c r="AB11" s="39" t="s">
         <v>2907</v>
       </c>
-      <c r="AC11" s="40" t="s">
+      <c r="AC11" s="39" t="s">
         <v>2908</v>
       </c>
-      <c r="AD11" s="40" t="s">
+      <c r="AD11" s="39" t="s">
         <v>2909</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="102">
-      <c r="A12" s="40">
+      <c r="A12" s="39">
         <v>32</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="39" t="s">
         <v>2910</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="39" t="s">
         <v>2911</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="39" t="s">
         <v>2912</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" s="39" t="s">
         <v>2913</v>
       </c>
-      <c r="J12" s="40" t="s">
+      <c r="J12" s="39" t="s">
         <v>2914</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" s="39" t="s">
         <v>2915</v>
       </c>
-      <c r="L12" s="40" t="s">
+      <c r="L12" s="39" t="s">
         <v>2916</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="39" t="s">
         <v>1300</v>
       </c>
-      <c r="N12" s="40" t="s">
+      <c r="N12" s="39" t="s">
         <v>2917</v>
       </c>
-      <c r="O12" s="40" t="s">
+      <c r="O12" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="P12" s="40" t="s">
+      <c r="P12" s="39" t="s">
         <v>2918</v>
       </c>
-      <c r="Q12" s="40" t="s">
+      <c r="Q12" s="39" t="s">
         <v>2919</v>
       </c>
-      <c r="R12" s="40" t="s">
+      <c r="R12" s="39" t="s">
         <v>2920</v>
       </c>
-      <c r="S12" s="40" t="s">
+      <c r="S12" s="39" t="s">
         <v>2921</v>
       </c>
-      <c r="T12" s="40" t="s">
+      <c r="T12" s="39" t="s">
         <v>2922</v>
       </c>
-      <c r="U12" s="40" t="s">
+      <c r="U12" s="39" t="s">
         <v>2923</v>
       </c>
-      <c r="V12" s="40" t="s">
+      <c r="V12" s="39" t="s">
         <v>2924</v>
       </c>
-      <c r="W12" s="40" t="s">
+      <c r="W12" s="39" t="s">
         <v>2925</v>
       </c>
-      <c r="X12" s="40" t="s">
+      <c r="X12" s="39" t="s">
         <v>2926</v>
       </c>
-      <c r="Y12" s="40" t="s">
+      <c r="Y12" s="39" t="s">
         <v>2927</v>
       </c>
-      <c r="Z12" s="40" t="s">
+      <c r="Z12" s="39" t="s">
         <v>2928</v>
       </c>
-      <c r="AA12" s="40" t="s">
+      <c r="AA12" s="39" t="s">
         <v>2929</v>
       </c>
-      <c r="AB12" s="40" t="s">
+      <c r="AB12" s="39" t="s">
         <v>2930</v>
       </c>
-      <c r="AC12" s="40" t="s">
+      <c r="AC12" s="39" t="s">
         <v>2931</v>
       </c>
-      <c r="AD12" s="40" t="s">
+      <c r="AD12" s="39" t="s">
         <v>2932</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="89.25">
-      <c r="A13" s="40">
+      <c r="A13" s="39">
         <v>33</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="39" t="s">
         <v>2933</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="39" t="s">
         <v>2934</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>2935</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="39" t="s">
         <v>2936</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="39" t="s">
         <v>2937</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" s="39" t="s">
         <v>2938</v>
       </c>
-      <c r="L13" s="40" t="s">
+      <c r="L13" s="39" t="s">
         <v>2939</v>
       </c>
-      <c r="M13" s="40" t="s">
+      <c r="M13" s="39" t="s">
         <v>2940</v>
       </c>
-      <c r="N13" s="40" t="s">
+      <c r="N13" s="39" t="s">
         <v>2941</v>
       </c>
-      <c r="O13" s="40" t="s">
+      <c r="O13" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="P13" s="40" t="s">
+      <c r="P13" s="39" t="s">
         <v>2942</v>
       </c>
-      <c r="Q13" s="40" t="s">
+      <c r="Q13" s="39" t="s">
         <v>2943</v>
       </c>
-      <c r="R13" s="40" t="s">
+      <c r="R13" s="39" t="s">
         <v>2944</v>
       </c>
-      <c r="S13" s="40" t="s">
+      <c r="S13" s="39" t="s">
         <v>2945</v>
       </c>
-      <c r="T13" s="40" t="s">
+      <c r="T13" s="39" t="s">
         <v>2946</v>
       </c>
-      <c r="U13" s="40" t="s">
+      <c r="U13" s="39" t="s">
         <v>2947</v>
       </c>
-      <c r="V13" s="40" t="s">
+      <c r="V13" s="39" t="s">
         <v>2948</v>
       </c>
-      <c r="W13" s="40" t="s">
+      <c r="W13" s="39" t="s">
         <v>2949</v>
       </c>
-      <c r="X13" s="40" t="s">
+      <c r="X13" s="39" t="s">
         <v>2950</v>
       </c>
-      <c r="Y13" s="40" t="s">
+      <c r="Y13" s="39" t="s">
         <v>2951</v>
       </c>
-      <c r="Z13" s="40" t="s">
+      <c r="Z13" s="39" t="s">
         <v>2952</v>
       </c>
-      <c r="AA13" s="40" t="s">
+      <c r="AA13" s="39" t="s">
         <v>2953</v>
       </c>
-      <c r="AB13" s="40" t="s">
+      <c r="AB13" s="39" t="s">
         <v>2954</v>
       </c>
-      <c r="AC13" s="40" t="s">
+      <c r="AC13" s="39" t="s">
         <v>2955</v>
       </c>
-      <c r="AD13" s="40" t="s">
+      <c r="AD13" s="39" t="s">
         <v>2956</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="102">
-      <c r="A14" s="40">
+      <c r="A14" s="39">
         <v>41</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="39" t="s">
         <v>2957</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="39" t="s">
         <v>2958</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>2959</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="39" t="s">
         <v>2960</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="39" t="s">
         <v>2961</v>
       </c>
-      <c r="J14" s="40" t="s">
+      <c r="J14" s="39" t="s">
         <v>2962</v>
       </c>
-      <c r="K14" s="40" t="s">
+      <c r="K14" s="39" t="s">
         <v>2963</v>
       </c>
-      <c r="L14" s="40" t="s">
+      <c r="L14" s="39" t="s">
         <v>2964</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="39" t="s">
         <v>2965</v>
       </c>
-      <c r="N14" s="40" t="s">
+      <c r="N14" s="39" t="s">
         <v>2966</v>
       </c>
-      <c r="O14" s="40" t="s">
+      <c r="O14" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="P14" s="40" t="s">
+      <c r="P14" s="39" t="s">
         <v>2967</v>
       </c>
-      <c r="Q14" s="40" t="s">
+      <c r="Q14" s="39" t="s">
         <v>2968</v>
       </c>
-      <c r="R14" s="40" t="s">
+      <c r="R14" s="39" t="s">
         <v>2969</v>
       </c>
-      <c r="S14" s="40" t="s">
+      <c r="S14" s="39" t="s">
         <v>2970</v>
       </c>
-      <c r="T14" s="40" t="s">
+      <c r="T14" s="39" t="s">
         <v>2971</v>
       </c>
-      <c r="U14" s="40" t="s">
+      <c r="U14" s="39" t="s">
         <v>2972</v>
       </c>
-      <c r="V14" s="40" t="s">
+      <c r="V14" s="39" t="s">
         <v>2973</v>
       </c>
-      <c r="W14" s="40" t="s">
+      <c r="W14" s="39" t="s">
         <v>2974</v>
       </c>
-      <c r="X14" s="40" t="s">
+      <c r="X14" s="39" t="s">
         <v>2975</v>
       </c>
-      <c r="Y14" s="40" t="s">
+      <c r="Y14" s="39" t="s">
         <v>2976</v>
       </c>
-      <c r="Z14" s="40" t="s">
+      <c r="Z14" s="39" t="s">
         <v>2977</v>
       </c>
-      <c r="AA14" s="40" t="s">
+      <c r="AA14" s="39" t="s">
         <v>2978</v>
       </c>
-      <c r="AB14" s="40" t="s">
+      <c r="AB14" s="39" t="s">
         <v>2979</v>
       </c>
-      <c r="AC14" s="40" t="s">
+      <c r="AC14" s="39" t="s">
         <v>2980</v>
       </c>
-      <c r="AD14" s="40" t="s">
+      <c r="AD14" s="39" t="s">
         <v>2981</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="102">
-      <c r="A15" s="40">
+      <c r="A15" s="39">
         <v>42</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="39" t="s">
         <v>2982</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="39" t="s">
         <v>2983</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>2984</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="39" t="s">
         <v>2985</v>
       </c>
-      <c r="J15" s="40" t="s">
+      <c r="J15" s="39" t="s">
         <v>2986</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" s="39" t="s">
         <v>2987</v>
       </c>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="39" t="s">
         <v>2988</v>
       </c>
-      <c r="M15" s="40" t="s">
+      <c r="M15" s="39" t="s">
         <v>2989</v>
       </c>
-      <c r="N15" s="40" t="s">
+      <c r="N15" s="39" t="s">
         <v>2990</v>
       </c>
-      <c r="O15" s="40" t="s">
+      <c r="O15" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="P15" s="40" t="s">
+      <c r="P15" s="39" t="s">
         <v>2991</v>
       </c>
-      <c r="Q15" s="40" t="s">
+      <c r="Q15" s="39" t="s">
         <v>2992</v>
       </c>
-      <c r="R15" s="40" t="s">
+      <c r="R15" s="39" t="s">
         <v>2993</v>
       </c>
-      <c r="S15" s="40" t="s">
+      <c r="S15" s="39" t="s">
         <v>2994</v>
       </c>
-      <c r="T15" s="40" t="s">
+      <c r="T15" s="39" t="s">
         <v>1498</v>
       </c>
-      <c r="U15" s="40" t="s">
+      <c r="U15" s="39" t="s">
         <v>2995</v>
       </c>
-      <c r="V15" s="40" t="s">
+      <c r="V15" s="39" t="s">
         <v>2996</v>
       </c>
-      <c r="W15" s="40" t="s">
+      <c r="W15" s="39" t="s">
         <v>2997</v>
       </c>
-      <c r="X15" s="40" t="s">
+      <c r="X15" s="39" t="s">
         <v>2998</v>
       </c>
-      <c r="Y15" s="40" t="s">
+      <c r="Y15" s="39" t="s">
         <v>2999</v>
       </c>
-      <c r="Z15" s="40" t="s">
+      <c r="Z15" s="39" t="s">
         <v>3000</v>
       </c>
-      <c r="AA15" s="40" t="s">
+      <c r="AA15" s="39" t="s">
         <v>3001</v>
       </c>
-      <c r="AB15" s="40" t="s">
+      <c r="AB15" s="39" t="s">
         <v>3002</v>
       </c>
-      <c r="AC15" s="40" t="s">
+      <c r="AC15" s="39" t="s">
         <v>3003</v>
       </c>
-      <c r="AD15" s="40" t="s">
+      <c r="AD15" s="39" t="s">
         <v>3004</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="102">
-      <c r="A16" s="40">
+      <c r="A16" s="39">
         <v>43</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="E16" s="40" t="s">
+      <c r="E16" s="39" t="s">
         <v>3005</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="39" t="s">
         <v>3006</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>3007</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="39" t="s">
         <v>3008</v>
       </c>
-      <c r="J16" s="40" t="s">
+      <c r="J16" s="39" t="s">
         <v>3009</v>
       </c>
-      <c r="K16" s="40" t="s">
+      <c r="K16" s="39" t="s">
         <v>3010</v>
       </c>
-      <c r="L16" s="40" t="s">
+      <c r="L16" s="39" t="s">
         <v>3011</v>
       </c>
-      <c r="M16" s="40" t="s">
+      <c r="M16" s="39" t="s">
         <v>1508</v>
       </c>
-      <c r="N16" s="40" t="s">
+      <c r="N16" s="39" t="s">
         <v>3012</v>
       </c>
-      <c r="O16" s="40" t="s">
+      <c r="O16" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="P16" s="40" t="s">
+      <c r="P16" s="39" t="s">
         <v>3013</v>
       </c>
-      <c r="Q16" s="40" t="s">
+      <c r="Q16" s="39" t="s">
         <v>3014</v>
       </c>
-      <c r="R16" s="40" t="s">
+      <c r="R16" s="39" t="s">
         <v>3015</v>
       </c>
-      <c r="S16" s="40" t="s">
+      <c r="S16" s="39" t="s">
         <v>3016</v>
       </c>
-      <c r="T16" s="40" t="s">
+      <c r="T16" s="39" t="s">
         <v>3017</v>
       </c>
-      <c r="U16" s="40" t="s">
+      <c r="U16" s="39" t="s">
         <v>3018</v>
       </c>
-      <c r="V16" s="40" t="s">
+      <c r="V16" s="39" t="s">
         <v>3019</v>
       </c>
-      <c r="W16" s="40" t="s">
+      <c r="W16" s="39" t="s">
         <v>3020</v>
       </c>
-      <c r="X16" s="40" t="s">
+      <c r="X16" s="39" t="s">
         <v>3021</v>
       </c>
-      <c r="Y16" s="40" t="s">
+      <c r="Y16" s="39" t="s">
         <v>3022</v>
       </c>
-      <c r="Z16" s="40" t="s">
+      <c r="Z16" s="39" t="s">
         <v>3023</v>
       </c>
-      <c r="AA16" s="40" t="s">
+      <c r="AA16" s="39" t="s">
         <v>3024</v>
       </c>
-      <c r="AB16" s="40" t="s">
+      <c r="AB16" s="39" t="s">
         <v>3025</v>
       </c>
-      <c r="AC16" s="40" t="s">
+      <c r="AC16" s="39" t="s">
         <v>3026</v>
       </c>
-      <c r="AD16" s="40" t="s">
+      <c r="AD16" s="39" t="s">
         <v>3027</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="89.25">
-      <c r="A17" s="40">
+      <c r="A17" s="39">
         <v>51</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="39" t="s">
         <v>3028</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="39" t="s">
         <v>3029</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="39" t="s">
         <v>3030</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="39" t="s">
         <v>3031</v>
       </c>
-      <c r="J17" s="40" t="s">
+      <c r="J17" s="39" t="s">
         <v>3032</v>
       </c>
-      <c r="K17" s="40" t="s">
+      <c r="K17" s="39" t="s">
         <v>3033</v>
       </c>
-      <c r="L17" s="40" t="s">
+      <c r="L17" s="39" t="s">
         <v>3034</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" s="39" t="s">
         <v>3035</v>
       </c>
-      <c r="N17" s="40" t="s">
+      <c r="N17" s="39" t="s">
         <v>3036</v>
       </c>
-      <c r="O17" s="40" t="s">
+      <c r="O17" s="39" t="s">
         <v>3037</v>
       </c>
-      <c r="P17" s="40" t="s">
+      <c r="P17" s="39" t="s">
         <v>3038</v>
       </c>
-      <c r="Q17" s="40" t="s">
+      <c r="Q17" s="39" t="s">
         <v>3039</v>
       </c>
-      <c r="R17" s="40" t="s">
+      <c r="R17" s="39" t="s">
         <v>3040</v>
       </c>
-      <c r="S17" s="40" t="s">
+      <c r="S17" s="39" t="s">
         <v>3041</v>
       </c>
-      <c r="T17" s="40" t="s">
+      <c r="T17" s="39" t="s">
         <v>3042</v>
       </c>
-      <c r="U17" s="40" t="s">
+      <c r="U17" s="39" t="s">
         <v>3043</v>
       </c>
-      <c r="V17" s="40" t="s">
+      <c r="V17" s="39" t="s">
         <v>3044</v>
       </c>
-      <c r="W17" s="40" t="s">
+      <c r="W17" s="39" t="s">
         <v>3045</v>
       </c>
-      <c r="X17" s="40" t="s">
+      <c r="X17" s="39" t="s">
         <v>3046</v>
       </c>
-      <c r="Y17" s="40" t="s">
+      <c r="Y17" s="39" t="s">
         <v>3047</v>
       </c>
-      <c r="Z17" s="40" t="s">
+      <c r="Z17" s="39" t="s">
         <v>3048</v>
       </c>
-      <c r="AA17" s="40" t="s">
+      <c r="AA17" s="39" t="s">
         <v>3049</v>
       </c>
-      <c r="AB17" s="40" t="s">
+      <c r="AB17" s="39" t="s">
         <v>3050</v>
       </c>
-      <c r="AC17" s="40" t="s">
+      <c r="AC17" s="39" t="s">
         <v>3051</v>
       </c>
-      <c r="AD17" s="40" t="s">
+      <c r="AD17" s="39" t="s">
         <v>3052</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="102">
-      <c r="A18" s="40">
+      <c r="A18" s="39">
         <v>52</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="39" t="s">
         <v>3053</v>
       </c>
-      <c r="F18" s="40" t="s">
+      <c r="F18" s="39" t="s">
         <v>3054</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="39" t="s">
         <v>3055</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="39" t="s">
         <v>3056</v>
       </c>
-      <c r="J18" s="40" t="s">
+      <c r="J18" s="39" t="s">
         <v>3057</v>
       </c>
-      <c r="K18" s="40" t="s">
+      <c r="K18" s="39" t="s">
         <v>3058</v>
       </c>
-      <c r="L18" s="40" t="s">
+      <c r="L18" s="39" t="s">
         <v>3059</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="39" t="s">
         <v>3060</v>
       </c>
-      <c r="N18" s="40" t="s">
+      <c r="N18" s="39" t="s">
         <v>3061</v>
       </c>
-      <c r="O18" s="40" t="s">
+      <c r="O18" s="39" t="s">
         <v>3062</v>
       </c>
-      <c r="P18" s="40" t="s">
+      <c r="P18" s="39" t="s">
         <v>3063</v>
       </c>
-      <c r="Q18" s="40" t="s">
+      <c r="Q18" s="39" t="s">
         <v>3064</v>
       </c>
-      <c r="R18" s="40" t="s">
+      <c r="R18" s="39" t="s">
         <v>3065</v>
       </c>
-      <c r="S18" s="40" t="s">
+      <c r="S18" s="39" t="s">
         <v>3066</v>
       </c>
-      <c r="T18" s="40" t="s">
+      <c r="T18" s="39" t="s">
         <v>3067</v>
       </c>
-      <c r="U18" s="40" t="s">
+      <c r="U18" s="39" t="s">
         <v>3068</v>
       </c>
-      <c r="V18" s="40" t="s">
+      <c r="V18" s="39" t="s">
         <v>3069</v>
       </c>
-      <c r="W18" s="40" t="s">
+      <c r="W18" s="39" t="s">
         <v>3070</v>
       </c>
-      <c r="X18" s="40" t="s">
+      <c r="X18" s="39" t="s">
         <v>3071</v>
       </c>
-      <c r="Y18" s="40" t="s">
+      <c r="Y18" s="39" t="s">
         <v>3072</v>
       </c>
-      <c r="Z18" s="40" t="s">
+      <c r="Z18" s="39" t="s">
         <v>1699</v>
       </c>
-      <c r="AA18" s="40" t="s">
+      <c r="AA18" s="39" t="s">
         <v>3073</v>
       </c>
-      <c r="AB18" s="40" t="s">
+      <c r="AB18" s="39" t="s">
         <v>3074</v>
       </c>
-      <c r="AC18" s="40" t="s">
+      <c r="AC18" s="39" t="s">
         <v>3075</v>
       </c>
-      <c r="AD18" s="40" t="s">
+      <c r="AD18" s="39" t="s">
         <v>3076</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="114.75">
-      <c r="A19" s="40">
+      <c r="A19" s="39">
         <v>53</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="39" t="s">
         <v>3077</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="39" t="s">
         <v>3078</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="39" t="s">
         <v>3079</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="39" t="s">
         <v>3080</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="J19" s="39" t="s">
         <v>3081</v>
       </c>
-      <c r="K19" s="40" t="s">
+      <c r="K19" s="39" t="s">
         <v>3082</v>
       </c>
-      <c r="L19" s="40" t="s">
+      <c r="L19" s="39" t="s">
         <v>3083</v>
       </c>
-      <c r="M19" s="40" t="s">
+      <c r="M19" s="39" t="s">
         <v>3084</v>
       </c>
-      <c r="N19" s="40" t="s">
+      <c r="N19" s="39" t="s">
         <v>3085</v>
       </c>
-      <c r="O19" s="40" t="s">
+      <c r="O19" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="P19" s="40" t="s">
+      <c r="P19" s="39" t="s">
         <v>3086</v>
       </c>
-      <c r="Q19" s="40" t="s">
+      <c r="Q19" s="39" t="s">
         <v>3087</v>
       </c>
-      <c r="R19" s="40" t="s">
+      <c r="R19" s="39" t="s">
         <v>3088</v>
       </c>
-      <c r="S19" s="40" t="s">
+      <c r="S19" s="39" t="s">
         <v>3089</v>
       </c>
-      <c r="T19" s="40" t="s">
+      <c r="T19" s="39" t="s">
         <v>3090</v>
       </c>
-      <c r="U19" s="40" t="s">
+      <c r="U19" s="39" t="s">
         <v>3091</v>
       </c>
-      <c r="V19" s="40" t="s">
+      <c r="V19" s="39" t="s">
         <v>3092</v>
       </c>
-      <c r="W19" s="40" t="s">
+      <c r="W19" s="39" t="s">
         <v>3093</v>
       </c>
-      <c r="X19" s="40" t="s">
+      <c r="X19" s="39" t="s">
         <v>3094</v>
       </c>
-      <c r="Y19" s="40" t="s">
+      <c r="Y19" s="39" t="s">
         <v>3095</v>
       </c>
-      <c r="Z19" s="40" t="s">
+      <c r="Z19" s="39" t="s">
         <v>1718</v>
       </c>
-      <c r="AA19" s="40" t="s">
+      <c r="AA19" s="39" t="s">
         <v>3096</v>
       </c>
-      <c r="AB19" s="40" t="s">
+      <c r="AB19" s="39" t="s">
         <v>3097</v>
       </c>
-      <c r="AC19" s="40" t="s">
+      <c r="AC19" s="39" t="s">
         <v>3098</v>
       </c>
-      <c r="AD19" s="40" t="s">
+      <c r="AD19" s="39" t="s">
         <v>3099</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="89.25">
-      <c r="A20" s="40">
+      <c r="A20" s="39">
         <v>61</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="39" t="s">
         <v>3100</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="39" t="s">
         <v>3101</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="39" t="s">
         <v>3102</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="39" t="s">
         <v>3103</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="39" t="s">
         <v>3104</v>
       </c>
-      <c r="K20" s="40" t="s">
+      <c r="K20" s="39" t="s">
         <v>3105</v>
       </c>
-      <c r="L20" s="40" t="s">
+      <c r="L20" s="39" t="s">
         <v>3106</v>
       </c>
-      <c r="M20" s="40" t="s">
+      <c r="M20" s="39" t="s">
         <v>1300</v>
       </c>
-      <c r="N20" s="40" t="s">
+      <c r="N20" s="39" t="s">
         <v>3107</v>
       </c>
-      <c r="O20" s="40" t="s">
+      <c r="O20" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="P20" s="40" t="s">
+      <c r="P20" s="39" t="s">
         <v>3108</v>
       </c>
-      <c r="Q20" s="40" t="s">
+      <c r="Q20" s="39" t="s">
         <v>3109</v>
       </c>
-      <c r="R20" s="40" t="s">
+      <c r="R20" s="39" t="s">
         <v>3110</v>
       </c>
-      <c r="S20" s="40" t="s">
+      <c r="S20" s="39" t="s">
         <v>3111</v>
       </c>
-      <c r="T20" s="40" t="s">
+      <c r="T20" s="39" t="s">
         <v>3112</v>
       </c>
-      <c r="U20" s="40" t="s">
+      <c r="U20" s="39" t="s">
         <v>3113</v>
       </c>
-      <c r="V20" s="40" t="s">
+      <c r="V20" s="39" t="s">
         <v>3114</v>
       </c>
-      <c r="W20" s="40" t="s">
+      <c r="W20" s="39" t="s">
         <v>3115</v>
       </c>
-      <c r="X20" s="40" t="s">
+      <c r="X20" s="39" t="s">
         <v>3116</v>
       </c>
-      <c r="Y20" s="40" t="s">
+      <c r="Y20" s="39" t="s">
         <v>3117</v>
       </c>
-      <c r="Z20" s="40" t="s">
+      <c r="Z20" s="39" t="s">
         <v>3118</v>
       </c>
-      <c r="AA20" s="40" t="s">
+      <c r="AA20" s="39" t="s">
         <v>3119</v>
       </c>
-      <c r="AB20" s="40" t="s">
+      <c r="AB20" s="39" t="s">
         <v>3120</v>
       </c>
-      <c r="AC20" s="40" t="s">
+      <c r="AC20" s="39" t="s">
         <v>3121</v>
       </c>
-      <c r="AD20" s="40" t="s">
+      <c r="AD20" s="39" t="s">
         <v>3122</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="102">
-      <c r="A21" s="40">
+      <c r="A21" s="39">
         <v>62</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="39" t="s">
         <v>3123</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="39" t="s">
         <v>3124</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="39" t="s">
         <v>3125</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="39" t="s">
         <v>3126</v>
       </c>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="39" t="s">
         <v>3127</v>
       </c>
-      <c r="K21" s="40" t="s">
+      <c r="K21" s="39" t="s">
         <v>3128</v>
       </c>
-      <c r="L21" s="40" t="s">
+      <c r="L21" s="39" t="s">
         <v>3129</v>
       </c>
-      <c r="M21" s="40" t="s">
+      <c r="M21" s="39" t="s">
         <v>3130</v>
       </c>
-      <c r="N21" s="40" t="s">
+      <c r="N21" s="39" t="s">
         <v>3131</v>
       </c>
-      <c r="O21" s="40" t="s">
+      <c r="O21" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="P21" s="40" t="s">
+      <c r="P21" s="39" t="s">
         <v>3132</v>
       </c>
-      <c r="Q21" s="40" t="s">
+      <c r="Q21" s="39" t="s">
         <v>3133</v>
       </c>
-      <c r="R21" s="40" t="s">
+      <c r="R21" s="39" t="s">
         <v>3134</v>
       </c>
-      <c r="S21" s="40" t="s">
+      <c r="S21" s="39" t="s">
         <v>3135</v>
       </c>
-      <c r="T21" s="40" t="s">
+      <c r="T21" s="39" t="s">
         <v>3136</v>
       </c>
-      <c r="U21" s="40" t="s">
+      <c r="U21" s="39" t="s">
         <v>3137</v>
       </c>
-      <c r="V21" s="40" t="s">
+      <c r="V21" s="39" t="s">
         <v>3138</v>
       </c>
-      <c r="W21" s="40" t="s">
+      <c r="W21" s="39" t="s">
         <v>3139</v>
       </c>
-      <c r="X21" s="40" t="s">
+      <c r="X21" s="39" t="s">
         <v>3140</v>
       </c>
-      <c r="Y21" s="40" t="s">
+      <c r="Y21" s="39" t="s">
         <v>3141</v>
       </c>
-      <c r="Z21" s="40" t="s">
+      <c r="Z21" s="39" t="s">
         <v>3142</v>
       </c>
-      <c r="AA21" s="40" t="s">
+      <c r="AA21" s="39" t="s">
         <v>3143</v>
       </c>
-      <c r="AB21" s="40" t="s">
+      <c r="AB21" s="39" t="s">
         <v>3144</v>
       </c>
-      <c r="AC21" s="40" t="s">
+      <c r="AC21" s="39" t="s">
         <v>3145</v>
       </c>
-      <c r="AD21" s="40" t="s">
+      <c r="AD21" s="39" t="s">
         <v>3146</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="89.25">
-      <c r="A22" s="40">
+      <c r="A22" s="39">
         <v>63</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="E22" s="39" t="s">
         <v>3147</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="39" t="s">
         <v>3148</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>3149</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="39" t="s">
         <v>3150</v>
       </c>
-      <c r="J22" s="40" t="s">
+      <c r="J22" s="39" t="s">
         <v>3151</v>
       </c>
-      <c r="K22" s="40" t="s">
+      <c r="K22" s="39" t="s">
         <v>3152</v>
       </c>
-      <c r="L22" s="40" t="s">
+      <c r="L22" s="39" t="s">
         <v>3153</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="39" t="s">
         <v>3154</v>
       </c>
-      <c r="N22" s="40" t="s">
+      <c r="N22" s="39" t="s">
         <v>3155</v>
       </c>
-      <c r="O22" s="40" t="s">
+      <c r="O22" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="P22" s="40" t="s">
+      <c r="P22" s="39" t="s">
         <v>3156</v>
       </c>
-      <c r="Q22" s="40" t="s">
+      <c r="Q22" s="39" t="s">
         <v>3157</v>
       </c>
-      <c r="R22" s="40" t="s">
+      <c r="R22" s="39" t="s">
         <v>3158</v>
       </c>
-      <c r="S22" s="40" t="s">
+      <c r="S22" s="39" t="s">
         <v>3159</v>
       </c>
-      <c r="T22" s="40" t="s">
+      <c r="T22" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="U22" s="40" t="s">
+      <c r="U22" s="39" t="s">
         <v>3160</v>
       </c>
-      <c r="V22" s="40" t="s">
+      <c r="V22" s="39" t="s">
         <v>3161</v>
       </c>
-      <c r="W22" s="40" t="s">
+      <c r="W22" s="39" t="s">
         <v>3162</v>
       </c>
-      <c r="X22" s="40" t="s">
+      <c r="X22" s="39" t="s">
         <v>3163</v>
       </c>
-      <c r="Y22" s="40" t="s">
+      <c r="Y22" s="39" t="s">
         <v>3164</v>
       </c>
-      <c r="Z22" s="40" t="s">
+      <c r="Z22" s="39" t="s">
         <v>3165</v>
       </c>
-      <c r="AA22" s="40" t="s">
+      <c r="AA22" s="39" t="s">
         <v>3166</v>
       </c>
-      <c r="AB22" s="40" t="s">
+      <c r="AB22" s="39" t="s">
         <v>3167</v>
       </c>
-      <c r="AC22" s="40" t="s">
+      <c r="AC22" s="39" t="s">
         <v>3168</v>
       </c>
-      <c r="AD22" s="40" t="s">
+      <c r="AD22" s="39" t="s">
         <v>3169</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="89.25">
-      <c r="A23" s="40">
+      <c r="A23" s="39">
         <v>71</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="39" t="s">
         <v>3170</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="39" t="s">
         <v>3171</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="39" t="s">
         <v>3172</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="39" t="s">
         <v>3173</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="39" t="s">
         <v>3174</v>
       </c>
-      <c r="K23" s="40" t="s">
+      <c r="K23" s="39" t="s">
         <v>3175</v>
       </c>
-      <c r="L23" s="40" t="s">
+      <c r="L23" s="39" t="s">
         <v>3176</v>
       </c>
-      <c r="M23" s="40" t="s">
+      <c r="M23" s="39" t="s">
         <v>3177</v>
       </c>
-      <c r="N23" s="40" t="s">
+      <c r="N23" s="39" t="s">
         <v>3178</v>
       </c>
-      <c r="O23" s="40" t="s">
+      <c r="O23" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="P23" s="40" t="s">
+      <c r="P23" s="39" t="s">
         <v>3179</v>
       </c>
-      <c r="Q23" s="40" t="s">
+      <c r="Q23" s="39" t="s">
         <v>3180</v>
       </c>
-      <c r="R23" s="40" t="s">
+      <c r="R23" s="39" t="s">
         <v>3181</v>
       </c>
-      <c r="S23" s="40" t="s">
+      <c r="S23" s="39" t="s">
         <v>3182</v>
       </c>
-      <c r="T23" s="40" t="s">
+      <c r="T23" s="39" t="s">
         <v>3183</v>
       </c>
-      <c r="U23" s="40" t="s">
+      <c r="U23" s="39" t="s">
         <v>3184</v>
       </c>
-      <c r="V23" s="40" t="s">
+      <c r="V23" s="39" t="s">
         <v>3185</v>
       </c>
-      <c r="W23" s="40" t="s">
+      <c r="W23" s="39" t="s">
         <v>3186</v>
       </c>
-      <c r="X23" s="40" t="s">
+      <c r="X23" s="39" t="s">
         <v>3187</v>
       </c>
-      <c r="Y23" s="40" t="s">
+      <c r="Y23" s="39" t="s">
         <v>3188</v>
       </c>
-      <c r="Z23" s="40" t="s">
+      <c r="Z23" s="39" t="s">
         <v>3189</v>
       </c>
-      <c r="AA23" s="40" t="s">
+      <c r="AA23" s="39" t="s">
         <v>3190</v>
       </c>
-      <c r="AB23" s="40" t="s">
+      <c r="AB23" s="39" t="s">
         <v>3191</v>
       </c>
-      <c r="AC23" s="40" t="s">
+      <c r="AC23" s="39" t="s">
         <v>3192</v>
       </c>
-      <c r="AD23" s="40" t="s">
+      <c r="AD23" s="39" t="s">
         <v>3193</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="89.25">
-      <c r="A24" s="40">
+      <c r="A24" s="39">
         <v>72</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="39" t="s">
         <v>3194</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="39" t="s">
         <v>3195</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="39" t="s">
         <v>3196</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="39" t="s">
         <v>3197</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="39" t="s">
         <v>3198</v>
       </c>
-      <c r="J24" s="40" t="s">
+      <c r="J24" s="39" t="s">
         <v>3199</v>
       </c>
-      <c r="K24" s="40" t="s">
+      <c r="K24" s="39" t="s">
         <v>3200</v>
       </c>
-      <c r="L24" s="40" t="s">
+      <c r="L24" s="39" t="s">
         <v>3201</v>
       </c>
-      <c r="M24" s="40" t="s">
+      <c r="M24" s="39" t="s">
         <v>3202</v>
       </c>
-      <c r="N24" s="40" t="s">
+      <c r="N24" s="39" t="s">
         <v>3203</v>
       </c>
-      <c r="O24" s="40" t="s">
+      <c r="O24" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="P24" s="40" t="s">
+      <c r="P24" s="39" t="s">
         <v>3204</v>
       </c>
-      <c r="Q24" s="40" t="s">
+      <c r="Q24" s="39" t="s">
         <v>3205</v>
       </c>
-      <c r="R24" s="40" t="s">
+      <c r="R24" s="39" t="s">
         <v>3206</v>
       </c>
-      <c r="S24" s="40" t="s">
+      <c r="S24" s="39" t="s">
         <v>3207</v>
       </c>
-      <c r="T24" s="40" t="s">
+      <c r="T24" s="39" t="s">
         <v>3208</v>
       </c>
-      <c r="U24" s="40" t="s">
+      <c r="U24" s="39" t="s">
         <v>3209</v>
       </c>
-      <c r="V24" s="40" t="s">
+      <c r="V24" s="39" t="s">
         <v>3210</v>
       </c>
-      <c r="W24" s="40" t="s">
+      <c r="W24" s="39" t="s">
         <v>3211</v>
       </c>
-      <c r="X24" s="40" t="s">
+      <c r="X24" s="39" t="s">
         <v>3212</v>
       </c>
-      <c r="Y24" s="40" t="s">
+      <c r="Y24" s="39" t="s">
         <v>3213</v>
       </c>
-      <c r="Z24" s="40" t="s">
+      <c r="Z24" s="39" t="s">
         <v>3214</v>
       </c>
-      <c r="AA24" s="40" t="s">
+      <c r="AA24" s="39" t="s">
         <v>3215</v>
       </c>
-      <c r="AB24" s="40" t="s">
+      <c r="AB24" s="39" t="s">
         <v>3216</v>
       </c>
-      <c r="AC24" s="40" t="s">
+      <c r="AC24" s="39" t="s">
         <v>3217</v>
       </c>
-      <c r="AD24" s="40" t="s">
+      <c r="AD24" s="39" t="s">
         <v>3218</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="102">
-      <c r="A25" s="40">
+      <c r="A25" s="39">
         <v>73</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="40" t="s">
+      <c r="E25" s="39" t="s">
         <v>3219</v>
       </c>
-      <c r="F25" s="40" t="s">
+      <c r="F25" s="39" t="s">
         <v>3220</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="39" t="s">
         <v>3221</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="39" t="s">
         <v>2769</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="39" t="s">
         <v>3222</v>
       </c>
-      <c r="J25" s="40" t="s">
+      <c r="J25" s="39" t="s">
         <v>3223</v>
       </c>
-      <c r="K25" s="40" t="s">
+      <c r="K25" s="39" t="s">
         <v>3224</v>
       </c>
-      <c r="L25" s="40" t="s">
+      <c r="L25" s="39" t="s">
         <v>3225</v>
       </c>
-      <c r="M25" s="40" t="s">
+      <c r="M25" s="39" t="s">
         <v>3226</v>
       </c>
-      <c r="N25" s="40" t="s">
+      <c r="N25" s="39" t="s">
         <v>3227</v>
       </c>
-      <c r="O25" s="40" t="s">
+      <c r="O25" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="P25" s="40" t="s">
+      <c r="P25" s="39" t="s">
         <v>3228</v>
       </c>
-      <c r="Q25" s="40" t="s">
+      <c r="Q25" s="39" t="s">
         <v>3229</v>
       </c>
-      <c r="R25" s="40" t="s">
+      <c r="R25" s="39" t="s">
         <v>3230</v>
       </c>
-      <c r="S25" s="40" t="s">
+      <c r="S25" s="39" t="s">
         <v>3231</v>
       </c>
-      <c r="T25" s="40" t="s">
+      <c r="T25" s="39" t="s">
         <v>3232</v>
       </c>
-      <c r="U25" s="40" t="s">
+      <c r="U25" s="39" t="s">
         <v>3233</v>
       </c>
-      <c r="V25" s="40" t="s">
+      <c r="V25" s="39" t="s">
         <v>3234</v>
       </c>
-      <c r="W25" s="40" t="s">
+      <c r="W25" s="39" t="s">
         <v>3235</v>
       </c>
-      <c r="X25" s="40" t="s">
+      <c r="X25" s="39" t="s">
         <v>3236</v>
       </c>
-      <c r="Y25" s="40" t="s">
+      <c r="Y25" s="39" t="s">
         <v>3237</v>
       </c>
-      <c r="Z25" s="40" t="s">
+      <c r="Z25" s="39" t="s">
         <v>2087</v>
       </c>
-      <c r="AA25" s="40" t="s">
+      <c r="AA25" s="39" t="s">
         <v>3238</v>
       </c>
-      <c r="AB25" s="40" t="s">
+      <c r="AB25" s="39" t="s">
         <v>3239</v>
       </c>
-      <c r="AC25" s="40" t="s">
+      <c r="AC25" s="39" t="s">
         <v>3240</v>
       </c>
-      <c r="AD25" s="40" t="s">
+      <c r="AD25" s="39" t="s">
         <v>3241</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25">
-      <c r="E26" s="41"/>
+      <c r="E26" s="40"/>
     </row>
     <row r="27" spans="1:30">
-      <c r="E27" s="42"/>
+      <c r="E27" s="41"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50027,7 +47708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E24076-17D2-437B-A3BB-3FCE6C3298FA}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
